--- a/Project Governance Tool Requirement_240726_Metrics_Updated 3.xlsx
+++ b/Project Governance Tool Requirement_240726_Metrics_Updated 3.xlsx
@@ -1,42 +1,45 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\Desktop 220626\Project Management Tool\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\ProjectGovernance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B4D2078C-E635-4F86-86FA-6EE7A4597BFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49945156-F01B-4BCC-AC00-99126BA1BCAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="897" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="897" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Architecture" sheetId="1" r:id="rId1"/>
-    <sheet name="Scope" sheetId="2" r:id="rId2"/>
-    <sheet name="Dash board" sheetId="3" r:id="rId3"/>
-    <sheet name="Project Charter" sheetId="4" r:id="rId4"/>
-    <sheet name="Project Status" sheetId="5" r:id="rId5"/>
-    <sheet name="Measurement" sheetId="6" r:id="rId6"/>
-    <sheet name="Contractual Compliance" sheetId="7" r:id="rId7"/>
-    <sheet name="Risk" sheetId="8" r:id="rId8"/>
-    <sheet name="Opportunity" sheetId="9" r:id="rId9"/>
-    <sheet name="Dependencies" sheetId="10" r:id="rId10"/>
-    <sheet name="Issues" sheetId="11" r:id="rId11"/>
-    <sheet name="Assumption" sheetId="12" r:id="rId12"/>
-    <sheet name="DE Assessment Form" sheetId="13" r:id="rId13"/>
-    <sheet name="Data Integrity" sheetId="14" r:id="rId14"/>
-    <sheet name="Integration" sheetId="15" r:id="rId15"/>
-    <sheet name="Security " sheetId="16" r:id="rId16"/>
-    <sheet name=" Login" sheetId="17" r:id="rId17"/>
-    <sheet name="Action" sheetId="18" r:id="rId18"/>
-    <sheet name="Requirements Elaboration" sheetId="19" r:id="rId19"/>
+    <sheet name="Changes" sheetId="20" r:id="rId2"/>
+    <sheet name="Defects" sheetId="21" r:id="rId3"/>
+    <sheet name="Scope" sheetId="2" r:id="rId4"/>
+    <sheet name="Dash board" sheetId="3" r:id="rId5"/>
+    <sheet name="Project Charter" sheetId="4" r:id="rId6"/>
+    <sheet name="Project Status" sheetId="5" r:id="rId7"/>
+    <sheet name="Measurement" sheetId="6" r:id="rId8"/>
+    <sheet name="Contractual Compliance" sheetId="7" r:id="rId9"/>
+    <sheet name="Risk" sheetId="8" r:id="rId10"/>
+    <sheet name="Opportunity" sheetId="9" r:id="rId11"/>
+    <sheet name="Dependencies" sheetId="10" r:id="rId12"/>
+    <sheet name="Issues" sheetId="11" r:id="rId13"/>
+    <sheet name="Assumption" sheetId="12" r:id="rId14"/>
+    <sheet name="DE Assessment Form" sheetId="13" r:id="rId15"/>
+    <sheet name="Data Integrity" sheetId="14" r:id="rId16"/>
+    <sheet name="Integration" sheetId="15" r:id="rId17"/>
+    <sheet name="Security " sheetId="16" r:id="rId18"/>
+    <sheet name=" Login" sheetId="17" r:id="rId19"/>
+    <sheet name="Action" sheetId="18" r:id="rId20"/>
+    <sheet name="Requirements Elaboration" sheetId="19" r:id="rId21"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId20"/>
+    <externalReference r:id="rId22"/>
   </externalReferences>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Changes!$A$1:$C$146</definedName>
     <definedName name="Phases">'[1]Hide '!$B$26:$B$31</definedName>
     <definedName name="Source">'[1]Hide '!$B$38:$B$43</definedName>
   </definedNames>
@@ -61,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1037" uniqueCount="583">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1400" uniqueCount="762">
   <si>
     <t>Project Type</t>
   </si>
@@ -1827,12 +1830,622 @@
     <t>Within -0.4 to 5 CP/ Manday. 
 0.45 CP/ Manday</t>
   </si>
+  <si>
+    <t>Module</t>
+  </si>
+  <si>
+    <t>Create Project</t>
+  </si>
+  <si>
+    <t>Oracle Project ID is mandatory. Right handside menu will be enabled only when Oracle ID is added. Bring it under new project and make it mandatory.</t>
+  </si>
+  <si>
+    <t>Closed</t>
+  </si>
+  <si>
+    <t>Project Reporting</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> AI Processing to be enabled. If AI data is available for the screen, then AI button will be enabled</t>
+  </si>
+  <si>
+    <t>Pending - Last</t>
+  </si>
+  <si>
+    <t>Maintain Project</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Project Type - Consulting to be added,  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Introduce Region field</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Remove Billing Type.</t>
+  </si>
+  <si>
+    <t>Add Critical Flag (Yes,N0o), Add Product Flag (Yes/No). If Product is Yes, Product Combo should be added.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Add Geo Head field in Delivery Team section. it should be defaulted.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> In Send for Approval, All the fields in Project Profile are mandatory. That should be validated</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Add Consulting type and measurement
+Effort Variation, Schedule Performance Index, Cost Performance Index</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Baseline and Formula to be added in measurement section (QA to provide)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Remove Engagement Type.</t>
+  </si>
+  <si>
+    <t>Amend Project</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> After Approval All the fields can be changes except Project Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Milestone should be renamed as Payment Milestone</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> RAIDO is non mandatory for Approval. Move RAIDO to a separate section (Project Register)</t>
+  </si>
+  <si>
+    <t>DE Flow</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> DE role to be developed. Approval should come to DE</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> DE to be removed from PM project charter. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PM -&gt; Sent To Approval DE -&gt; Approve / Reject</t>
+  </si>
+  <si>
+    <t>Main App</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Create Project, Report Project, Amend Project</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Remove Project Charter from Project Reporting (Weekly Reporting)</t>
+  </si>
+  <si>
+    <t>In Project Creation, Add Resource Allocated (Data will be pulled from Oracle on daily) under project Charter. In Project Reporting, Onsite and Offshore FTE should be fetched. Revenue should be fetched from Project Charter</t>
+  </si>
+  <si>
+    <t>Pending Integration / Testing / Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> In Monthly Review, have Measurements, Contractual compliance, RAIDO. Remove others</t>
+  </si>
+  <si>
+    <t>Action Tracker</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Action Tracker to be developed + Dashboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> DE assessment to be developed + Dashboard</t>
+  </si>
+  <si>
+    <t>General</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Process to track whether weekly report and monthly reports are submitted. Provision to view defaulter at all levels</t>
+  </si>
+  <si>
+    <t>My Summary</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> My Summary pages to be improved.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Measurement calculation to be implemented</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> For Commitment and Milestone, Actual field to be captured.</t>
+  </si>
+  <si>
+    <t>Project Health</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Develop Project Health dashboard. It should contain all reports and registers. {PROJECT LIST, RAG, RAIDO, METRICS, COMMITMENTS, PAYMENT MILESTONES, FINDINGS, ACTIONS, Data Integratyl etc}. Filters : Geo, Account, Project. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Add Applicable Phase should be added in Project Charter. Provision to select multiple phases with checkbox</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> In Project Amend section, project charter page, add Project Status combo (Ongoing, Hold, Closed, Open Only for Billing). </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Swap Leadership Support and Key Risks / Issues</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> RAG Status - Change it to Tab. Provision to pull from projects </t>
+  </si>
+  <si>
+    <t>Account Head Flow</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> In Account Manager Dashboard -- http://localhost:3000/dashboard/account-manager,
+	Project Governance Matrix - Rename Entity to Projects
+	- Add Account Column before projects</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Account Manager Dashboard, PM Dashboard and Geo Head Dashboard should be rename as My Summary for all roles</t>
+  </si>
+  <si>
+    <t>Account Reporting</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> In Account-Reporting, Above Account Reporting, Add Account Dashboard (Readonly) . Same as PPT.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Weeks should be populated with Monday date.</t>
+  </si>
+  <si>
+    <t>Geo Reporting</t>
+  </si>
+  <si>
+    <t>Implement geo reporting</t>
+  </si>
+  <si>
+    <t>CXO Flow</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cxo login: change geo review to geo dashboard</t>
+  </si>
+  <si>
+    <t>Geo Flow</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> geo login: Add New Menu - Geo Dashboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> acc login: Add New Menu - Acc Dashboard</t>
+  </si>
+  <si>
+    <t>CXO Dashboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Change the color to Blue.</t>
+  </si>
+  <si>
+    <t>Geo Dashboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> In Geo Dashboard, rename overview to Account Rollup</t>
+  </si>
+  <si>
+    <t>All</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Standard - Dashboard, Reporting</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Project Creation + Oracle Projects - Project Creation.</t>
+  </si>
+  <si>
+    <t>Remove Baseline Assessment from Create Project and Maintain Project menu. This is applicable only for Project Reporting.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Move AI Hub to top </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> DE Assessment - Alert should be removed. Finding should have Alert</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Action Tracker Implementation</t>
+  </si>
+  <si>
+    <t>Integrations</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> OneLogin Implementation</t>
+  </si>
+  <si>
+    <t>Deferred</t>
+  </si>
+  <si>
+    <t>In Grid, Add Geo and Account Name</t>
+  </si>
+  <si>
+    <t>Add Account RAG</t>
+  </si>
+  <si>
+    <t>Commitments Status</t>
+  </si>
+  <si>
+    <t>Breached should be added</t>
+  </si>
+  <si>
+    <t>Health Split - Remove Red, Orange, Green text</t>
+  </si>
+  <si>
+    <t>Open Actions - Use different color</t>
+  </si>
+  <si>
+    <t>Backend Loading</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Product List to be loaded </t>
+  </si>
+  <si>
+    <t>Acc Head can do PM jobs, Geo Head can do PM and Acct Head Job</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Amend Functionality:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Approved projects can be amended. All the fields except project type can be changed in amend.
+The value before amend is captured in Audit table. This Audit table is just for reference, no screen requried to view the changes.DE approval is requried in Amend. Edit Project button should be renamed as Amend Project. There is not send to approval button in Amend.
+All the Save &lt;&gt; should be renamed as Amend &lt;&gt;. Eg. Save Scope &amp; Schedule should be called  Amend Scope &amp; Schedule.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Valiations:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+On Approve:
+All the fields in Project Profile is mandatory
+In scope and schedule, All except project end date is mandatory
+All fields in measurement are mandatory
+There should be atleast one row in commitments and milestone
+RAIDO Registers are not mandatory. </t>
+    </r>
+  </si>
+  <si>
+    <t>Show Geo - Region in all places. Title should be Geo Region</t>
+  </si>
+  <si>
+    <t>There should be no restrict to approve and de assessment. It can be done any DE role. Name should be captured</t>
+  </si>
+  <si>
+    <t>Project Status reporting, Revenue and other details should be defaulted from previous period</t>
+  </si>
+  <si>
+    <t>Potential red should be handled in all places</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DE Flow should be changed. DE reporting to have DE Assement Date. </t>
+  </si>
+  <si>
+    <t>DE - View Project to be developed</t>
+  </si>
+  <si>
+    <t>Findings - Category. Align with RAG</t>
+  </si>
+  <si>
+    <t>Validations for Measurements. Range. Now I can give 200% for percentage measure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DE Assessment - Remove This Month and Last Assessment. Last Assessment date should be shown with Due </t>
+  </si>
+  <si>
+    <t>Finding should be at project level</t>
+  </si>
+  <si>
+    <t>Add DE findings in the left hand side. Findings can be created with or without assessment</t>
+  </si>
+  <si>
+    <t>There should be a provision to view previous assessment</t>
+  </si>
+  <si>
+    <t>For Partial Project Profile, % is not computed properly</t>
+  </si>
+  <si>
+    <t>In project profile, delivery manager should be defaulted</t>
+  </si>
+  <si>
+    <t>In Scope, Plan End date is mandatory</t>
+  </si>
+  <si>
+    <t>Mandatory * to be added without validations</t>
+  </si>
+  <si>
+    <t>New Commitment and payment milestones can be added only in Amend. Remove Add functionality from Project Reporting</t>
+  </si>
+  <si>
+    <t>In New Project, Remove right side menu. http://localhost:3000/new-project/new/create</t>
+  </si>
+  <si>
+    <t>Move Maintain project next to New Project</t>
+  </si>
+  <si>
+    <t>Create Project, Provide Project Details, Amend Project Details,  Report Project Status, Project Dashboard  - PM Menu</t>
+  </si>
+  <si>
+    <t>Weekly Report - Delivery Status Reporting (Weekly)
+Monlthly Report - Metrics Reporting (Monthly)</t>
+  </si>
+  <si>
+    <t>VAPT testing</t>
+  </si>
+  <si>
+    <t>Functional Testing</t>
+  </si>
+  <si>
+    <t>Server Provisioning</t>
+  </si>
+  <si>
+    <t>Project Team Testing</t>
+  </si>
+  <si>
+    <t>Load Account and User details. Check all admin page data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finding should be added as Left Side menu for PM. </t>
+  </si>
+  <si>
+    <t>Finding total should be shown to Account Head, Geo Head and CXO</t>
+  </si>
+  <si>
+    <t>For Metics validation, Need lower limit, upper limit and breach limit. When the value is greater than breach limit, what should we do?</t>
+  </si>
+  <si>
+    <t>Finding will be raised against Project, no assignee is requried</t>
+  </si>
+  <si>
+    <t>Findings - Current classificaiton should be called Category. New Classificaiton - Observation/ Recommendation/NC. Remove Criticality</t>
+  </si>
+  <si>
+    <t>PM Menu - Rename Findings as DE Findings</t>
+  </si>
+  <si>
+    <t>PM Findings - Remarks to be renamed as Action Taken. Add Action Taken Date</t>
+  </si>
+  <si>
+    <t>DE Findings Closure - Add Closure Date, Verification Remarks. Remove Save Changes. Add Reopen Findings</t>
+  </si>
+  <si>
+    <t>Applicable Phases -  Discovery / POC / Assessment / Consulting (First) , Migration (Last) , UAT to UAT Support</t>
+  </si>
+  <si>
+    <t>In http://localhost:3000/project-health/project-list, Add Region and Ownership in Filter and grid</t>
+  </si>
+  <si>
+    <t>http://localhost:3000/project-health/findings - Add Classification filter and Over Due and Non Over Due Filter.</t>
+  </si>
+  <si>
+    <t>Project health grid should have download to excel feature</t>
+  </si>
+  <si>
+    <t>Against a commitment, there should be a provision to record multiple actuals</t>
+  </si>
+  <si>
+    <t>In Account Reporting and Geo Reporting, Remove monthly reporting</t>
+  </si>
+  <si>
+    <t>Executive Risk Dashboard</t>
+  </si>
+  <si>
+    <t>Pending with Quality</t>
+  </si>
+  <si>
+    <t>Not submitted - Red, Submitted - Green. This is for all reports</t>
+  </si>
+  <si>
+    <t>Project, Account, Geo should have Governance Tool Implementation Effective Date. Pending reports should be computed based on this date</t>
+  </si>
+  <si>
+    <t>Weekly Reporting and Monthly reporting should be replaced with Delivery reporting and Metric reporting</t>
+  </si>
+  <si>
+    <t>NC should renamed as Alert</t>
+  </si>
+  <si>
+    <t>Delivery Status Reporting is the common name. Tag Project, Account or Geo</t>
+  </si>
+  <si>
+    <t>In DE Projects Measurements should have Reporting period, Contractual compliance - Actual value to be displayed,</t>
+  </si>
+  <si>
+    <t>RAIDO register should have filter in PM and DE Views</t>
+  </si>
+  <si>
+    <t>In Findings all fields are mandatory</t>
+  </si>
+  <si>
+    <t>In Findings Page, Project should be auto complete text box instead of combo</t>
+  </si>
+  <si>
+    <t>In all project filters, add Geo, Region, Account, Type and Ownership</t>
+  </si>
+  <si>
+    <t>In Compliance, Status Breached should be removed. penality column should be shown in compliance history grid</t>
+  </si>
+  <si>
+    <t>PM Assignment AutoText to be moved to Create Project Details. PM in create project details should be Readonly</t>
+  </si>
+  <si>
+    <t>Assignment of roles and names for Geo, Account and Project should be provided for Geo Heads and DE</t>
+  </si>
+  <si>
+    <t>Create project should be enabled only for Geo Head and Acc Heads</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create Project - Workflow Approval to DE </t>
+  </si>
+  <si>
+    <t>Archive Project for DE should be enabled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project Health should have report submissions summaries </t>
+  </si>
+  <si>
+    <t>Notification in App functionality to be implemented</t>
+  </si>
+  <si>
+    <t>In Measurement - Metrics Target, info icon should be shown</t>
+  </si>
+  <si>
+    <t>In Measurement - Metrics Target, Productivity UOM should be loaded from config. It is displayed wrongly</t>
+  </si>
+  <si>
+    <t>In Measurement - Metrics Target, Benchmark value should be loaded from config</t>
+  </si>
+  <si>
+    <t>In Create Project, PM combo should be filtered combo</t>
+  </si>
+  <si>
+    <t>In DE Menu, rename Project Creation Requests to Project Creation Approval and DE Approval to Project Details Approval</t>
+  </si>
+  <si>
+    <t>For Accounts, Region should be captured.</t>
+  </si>
+  <si>
+    <t>In DE Menu, rename Projects as View Projects and Project Health as View Project Health</t>
+  </si>
+  <si>
+    <t>Tool Name, Login page, BCT Logo and Tag line to be added</t>
+  </si>
+  <si>
+    <t>Change password and forgot password feature to be implemented</t>
+  </si>
+  <si>
+    <t>Project Creation Approval and Rejection should have Remarks</t>
+  </si>
+  <si>
+    <t>When Project is Created, Org, Geo, Region and Account to be fetched based on Oracle Id, can be changed before saving</t>
+  </si>
+  <si>
+    <t>In Development Metrics, Size Unit - Add Story Point. On change of Size Unit, Productivity should be changed</t>
+  </si>
+  <si>
+    <t>In Development Metrics, Overall Effort esmitate, unit should be person-day</t>
+  </si>
+  <si>
+    <t>Commitment should have UOM as textbox</t>
+  </si>
+  <si>
+    <t>DE Allocation is not mandatory. Project Details Approval can be done without DE</t>
+  </si>
+  <si>
+    <t>When Project is rejected, Rejection remarks should be shown. DE status should be shown in the Grid</t>
+  </si>
+  <si>
+    <t>Notifcation to be checked</t>
+  </si>
+  <si>
+    <t>When the Project is Approved, the lifecycle status should be OnGoing</t>
+  </si>
+  <si>
+    <t>Open Alerts till the reporting period should be brought in the dashboards. After submission, the report should be frozen, values should not change</t>
+  </si>
+  <si>
+    <t>Project Reporting, There should be a provision to resubmit the project report after rejection</t>
+  </si>
+  <si>
+    <t>DE Assessment Report should be added in PM View. Same as http://192.168.1.175:3000/de-assessment/4f2e19c4-7b99-4ddf-bfb9-49a97d7c0ae2. All fields readonly</t>
+  </si>
+  <si>
+    <t>Metics report should be renamed as Project Performance Report. There is not approval process. In all pages, Reviewed and No Changes button to added. This marks the completion of the review process</t>
+  </si>
+  <si>
+    <t>Project Performance Dashboard to be developed</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>In Account Manager view, Project Dashboard to be renamed as Delivery Status Report.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> New Menu, Project Performance Report to be added </t>
+    </r>
+  </si>
+  <si>
+    <t>Pending</t>
+  </si>
+  <si>
+    <t>In DE Allocation, there should be a provision to fetch DE allocated project and DE can be changed any time.</t>
+  </si>
+  <si>
+    <t>In Account Reporting, Submit Report should be enabled only from Dashboard. It should be removed from Account Status. This should be done for Geo Reporting also</t>
+  </si>
+  <si>
+    <t>In Account Reporting main page, Report status should be rejected for Rejected reports. There should be a provision to resubmit the rejeccted report. Check for Project Reporting and Geo Reporting</t>
+  </si>
+  <si>
+    <t>CXO should be renamed as CDO</t>
+  </si>
+  <si>
+    <t>In All Pages, Project Dashboard should be renamed as Delivery Status Report &amp; Project Performance Report</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Action Flow - </t>
+  </si>
+  <si>
+    <t>New Action Creation / View Page from Left Menu</t>
+  </si>
+  <si>
+    <t>DE Menu - Project Health - To view project , account , geo reports</t>
+  </si>
+  <si>
+    <t>In Geo Head Reporting, Executive update is not launching. In 175 server, this issue is simulated</t>
+  </si>
+  <si>
+    <t>Project Performance Dashboard -- from View pages, back should take to main page. Breadcrumb to be updated</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2002,6 +2615,20 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="7"/>
+      <color theme="1"/>
+      <name val="Geist"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -2807,13 +3434,14 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="272">
+  <cellXfs count="270">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3203,46 +3831,80 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="3" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3250,34 +3912,23 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3285,13 +3936,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3300,43 +3957,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="4" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="5">
     <cellStyle name="Excel Built-in Normal" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="Hyperlink" xfId="4" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Normal 3" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
@@ -3799,195 +4432,269 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="B3:C24"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="C4:G33"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="24.54296875" customWidth="1"/>
-    <col min="3" max="3" width="32.54296875" customWidth="1"/>
+    <col min="3" max="3" width="24.21875" customWidth="1"/>
+    <col min="4" max="4" width="23.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B3" s="129" t="s">
+    <row r="4" spans="3:5">
+      <c r="C4" s="129" t="s">
         <v>344</v>
       </c>
-      <c r="C3" s="129" t="s">
+      <c r="D4" s="129" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B4" s="31" t="s">
-        <v>426</v>
-      </c>
-      <c r="C4" s="31" t="s">
+    <row r="5" spans="3:5">
+      <c r="C5" s="31" t="s">
+        <v>345</v>
+      </c>
+      <c r="D5" s="31" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B5" s="31" t="s">
+      <c r="E5" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="6" spans="3:5">
+      <c r="C6" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="31" t="s">
+      <c r="D6" s="31" t="s">
         <v>348</v>
       </c>
-    </row>
-    <row r="6" spans="2:3" ht="72.650000000000006" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="31" t="s">
+      <c r="E6" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="7" spans="3:5" ht="101.55" customHeight="1">
+      <c r="C7" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="31" t="s">
+      <c r="D7" s="31" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B7" s="31" t="s">
-        <v>427</v>
-      </c>
-      <c r="C7" s="31" t="s">
+      <c r="E7" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="8" spans="3:5">
+      <c r="C8" s="31" t="s">
+        <v>350</v>
+      </c>
+      <c r="D8" s="31" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B8" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C8" s="31" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="9" spans="2:3" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="31" t="s">
-        <v>429</v>
-      </c>
+    <row r="9" spans="3:5">
       <c r="C9" s="31" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="10" spans="2:3" ht="29.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="31" t="s">
-        <v>404</v>
-      </c>
+        <v>352</v>
+      </c>
+      <c r="D9" s="31" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="10" spans="3:5" ht="43.5" customHeight="1">
       <c r="C10" s="31" t="s">
+        <v>354</v>
+      </c>
+      <c r="D10" s="31" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="11" spans="2:3" ht="29.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="31" t="s">
-        <v>431</v>
-      </c>
+    <row r="11" spans="3:5">
       <c r="C11" s="31" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B12" s="31" t="s">
-        <v>433</v>
-      </c>
+        <v>356</v>
+      </c>
+      <c r="D11" s="31" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="12" spans="3:5">
       <c r="C12" s="31" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B13" s="31" t="s">
-        <v>435</v>
-      </c>
+        <v>358</v>
+      </c>
+      <c r="D12" s="31" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="13" spans="3:5">
       <c r="C13" s="31" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="14" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B14" s="31" t="s">
-        <v>437</v>
-      </c>
+        <v>360</v>
+      </c>
+      <c r="D13" s="31" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="14" spans="3:5">
       <c r="C14" s="31" t="s">
+        <v>362</v>
+      </c>
+      <c r="D14" s="31" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="15" spans="2:3" ht="29.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="31" t="s">
-        <v>438</v>
-      </c>
+    <row r="15" spans="3:5" ht="29.1" customHeight="1">
       <c r="C15" s="31" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="16" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B16" s="31" t="s">
-        <v>440</v>
-      </c>
+        <v>364</v>
+      </c>
+      <c r="D15" s="31" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="16" spans="3:5" ht="29.1" customHeight="1">
       <c r="C16" s="31" t="s">
+        <v>366</v>
+      </c>
+      <c r="D16" s="31" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="17" spans="3:7" ht="29.1" customHeight="1">
+      <c r="C17" s="31" t="s">
+        <v>368</v>
+      </c>
+      <c r="D17" s="31" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="18" spans="3:7">
+      <c r="C18" s="31" t="s">
+        <v>370</v>
+      </c>
+      <c r="D18" s="31" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="19" spans="3:7">
+      <c r="C19" s="31" t="s">
+        <v>372</v>
+      </c>
+      <c r="D19" s="31" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B17" s="31" t="s">
-        <v>441</v>
-      </c>
-      <c r="C17" s="31" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B18" s="31" t="s">
-        <v>443</v>
-      </c>
-      <c r="C18" s="31" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B19" s="31" t="s">
+    <row r="20" spans="3:7">
+      <c r="C20" s="31" t="s">
+        <v>374</v>
+      </c>
+      <c r="D20" s="31" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="21" spans="3:7">
+      <c r="C21" s="31" t="s">
+        <v>376</v>
+      </c>
+      <c r="D21" s="31" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="22" spans="3:7" ht="29.1" customHeight="1">
+      <c r="C22" s="31" t="s">
+        <v>378</v>
+      </c>
+      <c r="D22" s="31" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="23" spans="3:7">
+      <c r="C23" s="31" t="s">
         <v>380</v>
       </c>
-      <c r="C19" s="31" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B20" s="31" t="s">
+      <c r="D23" s="31" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="24" spans="3:7">
+      <c r="C24" s="31" t="s">
+        <v>382</v>
+      </c>
+      <c r="D24" s="31" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="25" spans="3:7" ht="29.1" customHeight="1">
+      <c r="C25" s="31" t="s">
+        <v>384</v>
+      </c>
+      <c r="D25" s="31" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="26" spans="3:7">
+      <c r="C26" s="31" t="s">
+        <v>386</v>
+      </c>
+      <c r="D26" s="31" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="27" spans="3:7">
+      <c r="C27" s="31" t="s">
+        <v>388</v>
+      </c>
+      <c r="D27" s="31" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="28" spans="3:7">
+      <c r="C28" s="31" t="s">
         <v>390</v>
       </c>
-      <c r="C20" s="31" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="21" spans="2:3" ht="29.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="31" t="s">
-        <v>447</v>
-      </c>
-      <c r="C21" s="31" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B22" s="31" t="s">
-        <v>449</v>
-      </c>
-      <c r="C22" s="31" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B23" s="31" t="s">
-        <v>451</v>
-      </c>
-      <c r="C23" s="31" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B24" s="31" t="s">
+      <c r="D28" s="31" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="29" spans="3:7">
+      <c r="C29" s="31" t="s">
+        <v>392</v>
+      </c>
+      <c r="D29" s="31" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="30" spans="3:7">
+      <c r="C30" s="31" t="s">
+        <v>394</v>
+      </c>
+      <c r="D30" s="31" t="s">
+        <v>395</v>
+      </c>
+      <c r="G30" s="33"/>
+    </row>
+    <row r="31" spans="3:7">
+      <c r="C31" s="31" t="s">
+        <v>396</v>
+      </c>
+      <c r="D31" s="31" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="32" spans="3:7">
+      <c r="C32" s="31" t="s">
+        <v>398</v>
+      </c>
+      <c r="D32" s="31" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="33" spans="3:4">
+      <c r="C33" s="31" t="s">
         <v>342</v>
       </c>
-      <c r="C24" s="31" t="s">
-        <v>453</v>
+      <c r="D33" s="31" t="s">
+        <v>400</v>
       </c>
     </row>
   </sheetData>
@@ -3996,15 +4703,15 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="B3:C28"/>
-  <sheetFormatPr defaultColWidth="12.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="B3:C25"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="19.453125" customWidth="1"/>
-    <col min="3" max="3" width="28.453125" customWidth="1"/>
+    <col min="2" max="2" width="15.77734375" customWidth="1"/>
+    <col min="3" max="3" width="24.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:3">
       <c r="B3" s="129" t="s">
         <v>344</v>
       </c>
@@ -4012,15 +4719,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:3">
       <c r="B4" s="31" t="s">
-        <v>454</v>
+        <v>401</v>
       </c>
       <c r="C4" s="31" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:3">
       <c r="B5" s="31" t="s">
         <v>29</v>
       </c>
@@ -4028,7 +4735,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="6" spans="2:3" ht="72.650000000000006" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:3" ht="101.55" customHeight="1">
       <c r="B6" s="31" t="s">
         <v>0</v>
       </c>
@@ -4036,179 +4743,155 @@
         <v>55</v>
       </c>
     </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:3">
       <c r="B7" s="31" t="s">
-        <v>455</v>
+        <v>402</v>
       </c>
       <c r="C7" s="31" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:3" ht="29.1" customHeight="1">
       <c r="B8" s="31" t="s">
-        <v>456</v>
+        <v>403</v>
       </c>
       <c r="C8" s="31" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="9" spans="2:3" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:3" ht="43.5" customHeight="1">
       <c r="B9" s="31" t="s">
-        <v>457</v>
+        <v>404</v>
       </c>
       <c r="C9" s="31" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:3" ht="29.1" customHeight="1">
       <c r="B10" s="31" t="s">
-        <v>458</v>
+        <v>358</v>
       </c>
       <c r="C10" s="31" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.35">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3">
       <c r="B11" s="31" t="s">
-        <v>372</v>
+        <v>360</v>
       </c>
       <c r="C11" s="31" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.35">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3" ht="29.1" customHeight="1">
       <c r="B12" s="31" t="s">
-        <v>460</v>
+        <v>406</v>
       </c>
       <c r="C12" s="31" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.35">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3" ht="29.1" customHeight="1">
       <c r="B13" s="31" t="s">
-        <v>462</v>
+        <v>368</v>
       </c>
       <c r="C13" s="31" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="14" spans="2:3" x14ac:dyDescent="0.35">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3" ht="29.1" customHeight="1">
       <c r="B14" s="31" t="s">
-        <v>464</v>
+        <v>408</v>
       </c>
       <c r="C14" s="31" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="15" spans="2:3" x14ac:dyDescent="0.35">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3">
       <c r="B15" s="31" t="s">
-        <v>465</v>
+        <v>410</v>
       </c>
       <c r="C15" s="31" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="16" spans="2:3" x14ac:dyDescent="0.35">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3" ht="58.05" customHeight="1">
       <c r="B16" s="31" t="s">
-        <v>467</v>
+        <v>412</v>
       </c>
       <c r="C16" s="31" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.35">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" ht="29.1" customHeight="1">
       <c r="B17" s="31" t="s">
-        <v>374</v>
+        <v>414</v>
       </c>
       <c r="C17" s="31" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.35">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3">
       <c r="B18" s="31" t="s">
-        <v>376</v>
+        <v>416</v>
       </c>
       <c r="C18" s="31" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.35">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" ht="43.5" customHeight="1">
       <c r="B19" s="31" t="s">
-        <v>470</v>
+        <v>418</v>
       </c>
       <c r="C19" s="31" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.35">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" ht="29.1" customHeight="1">
       <c r="B20" s="31" t="s">
-        <v>472</v>
+        <v>341</v>
       </c>
       <c r="C20" s="31" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="21" spans="2:3" ht="29.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" ht="29.1" customHeight="1">
       <c r="B21" s="31" t="s">
-        <v>474</v>
+        <v>420</v>
       </c>
       <c r="C21" s="31" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="22" spans="2:3" ht="29.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3">
       <c r="B22" s="31" t="s">
-        <v>341</v>
+        <v>421</v>
       </c>
       <c r="C22" s="31" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="23" spans="2:3" ht="29.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3">
       <c r="B23" s="31" t="s">
-        <v>447</v>
+        <v>423</v>
       </c>
       <c r="C23" s="31" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.35">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3">
       <c r="B24" s="31" t="s">
-        <v>478</v>
+        <v>398</v>
       </c>
       <c r="C24" s="31" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.35">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3">
       <c r="B25" s="31" t="s">
-        <v>480</v>
+        <v>342</v>
       </c>
       <c r="C25" s="31" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B26" s="31" t="s">
-        <v>482</v>
-      </c>
-      <c r="C26" s="31" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B27" s="31" t="s">
-        <v>398</v>
-      </c>
-      <c r="C27" s="31" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B28" s="31" t="s">
-        <v>342</v>
-      </c>
-      <c r="C28" s="31" t="s">
         <v>400</v>
       </c>
     </row>
@@ -4218,179 +4901,187 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
-  <dimension ref="B2:C22"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+  <dimension ref="B3:C24"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="27.1796875" customWidth="1"/>
-    <col min="3" max="3" width="41.7265625" customWidth="1"/>
+    <col min="2" max="2" width="24.5546875" customWidth="1"/>
+    <col min="3" max="3" width="32.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B2" s="129" t="s">
+    <row r="3" spans="2:3">
+      <c r="B3" s="129" t="s">
         <v>344</v>
       </c>
-      <c r="C2" s="129" t="s">
+      <c r="C3" s="129" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B3" s="31" t="s">
-        <v>484</v>
-      </c>
-      <c r="C3" s="31" t="s">
+    <row r="4" spans="2:3">
+      <c r="B4" s="31" t="s">
+        <v>426</v>
+      </c>
+      <c r="C4" s="31" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B4" s="31" t="s">
+    <row r="5" spans="2:3">
+      <c r="B5" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="31" t="s">
+      <c r="C5" s="31" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="5" spans="2:3" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="31" t="s">
+    <row r="6" spans="2:3" ht="72.599999999999994" customHeight="1">
+      <c r="B6" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="31" t="s">
+      <c r="C6" s="31" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B6" s="31" t="s">
-        <v>485</v>
-      </c>
-      <c r="C6" s="31" t="s">
+    <row r="7" spans="2:3">
+      <c r="B7" s="31" t="s">
+        <v>427</v>
+      </c>
+      <c r="C7" s="31" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B7" s="31" t="s">
-        <v>486</v>
-      </c>
-      <c r="C7" s="31" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="8" spans="2:3" ht="29.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:3">
       <c r="B8" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" s="31" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" ht="43.5" customHeight="1">
+      <c r="B9" s="31" t="s">
+        <v>429</v>
+      </c>
+      <c r="C9" s="31" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" ht="29.1" customHeight="1">
+      <c r="B10" s="31" t="s">
         <v>404</v>
       </c>
-      <c r="C8" s="31" t="s">
+      <c r="C10" s="31" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B9" s="31" t="s">
-        <v>460</v>
-      </c>
-      <c r="C9" s="31" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B10" s="31" t="s">
-        <v>462</v>
-      </c>
-      <c r="C10" s="31" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:3" ht="29.1" customHeight="1">
       <c r="B11" s="31" t="s">
+        <v>431</v>
+      </c>
+      <c r="C11" s="31" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3">
+      <c r="B12" s="31" t="s">
+        <v>433</v>
+      </c>
+      <c r="C12" s="31" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3">
+      <c r="B13" s="31" t="s">
+        <v>435</v>
+      </c>
+      <c r="C13" s="31" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3">
+      <c r="B14" s="31" t="s">
         <v>437</v>
       </c>
-      <c r="C11" s="31" t="s">
+      <c r="C14" s="31" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B12" s="31" t="s">
-        <v>490</v>
-      </c>
-      <c r="C12" s="31" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B13" s="31" t="s">
-        <v>492</v>
-      </c>
-      <c r="C13" s="31" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="14" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B14" s="31" t="s">
-        <v>494</v>
-      </c>
-      <c r="C14" s="31" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="15" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:3" ht="29.1" customHeight="1">
       <c r="B15" s="31" t="s">
-        <v>496</v>
+        <v>438</v>
       </c>
       <c r="C15" s="31" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="16" spans="2:3" x14ac:dyDescent="0.35">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3">
       <c r="B16" s="31" t="s">
-        <v>498</v>
+        <v>440</v>
       </c>
       <c r="C16" s="31" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.35">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3">
       <c r="B17" s="31" t="s">
-        <v>500</v>
+        <v>441</v>
       </c>
       <c r="C17" s="31" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.35">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3">
       <c r="B18" s="31" t="s">
+        <v>443</v>
+      </c>
+      <c r="C18" s="31" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3">
+      <c r="B19" s="31" t="s">
         <v>380</v>
       </c>
-      <c r="C18" s="31" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B19" s="31" t="s">
-        <v>382</v>
-      </c>
       <c r="C19" s="31" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.35">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3">
       <c r="B20" s="31" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C20" s="31" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.35">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" ht="29.1" customHeight="1">
       <c r="B21" s="31" t="s">
+        <v>447</v>
+      </c>
+      <c r="C21" s="31" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3">
+      <c r="B22" s="31" t="s">
+        <v>449</v>
+      </c>
+      <c r="C22" s="31" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3">
+      <c r="B23" s="31" t="s">
         <v>451</v>
       </c>
-      <c r="C21" s="31" t="s">
+      <c r="C23" s="31" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B22" s="31" t="s">
+    <row r="24" spans="2:3">
+      <c r="B24" s="31" t="s">
         <v>342</v>
       </c>
-      <c r="C22" s="31" t="s">
+      <c r="C24" s="31" t="s">
         <v>453</v>
       </c>
     </row>
@@ -4400,81 +5091,485 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+  <dimension ref="B3:C28"/>
+  <sheetFormatPr defaultColWidth="12.77734375" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="19.44140625" customWidth="1"/>
+    <col min="3" max="3" width="28.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:3">
+      <c r="B3" s="129" t="s">
+        <v>344</v>
+      </c>
+      <c r="C3" s="129" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3">
+      <c r="B4" s="31" t="s">
+        <v>454</v>
+      </c>
+      <c r="C4" s="31" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3">
+      <c r="B5" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="31" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" ht="72.599999999999994" customHeight="1">
+      <c r="B6" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="31" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3">
+      <c r="B7" s="31" t="s">
+        <v>455</v>
+      </c>
+      <c r="C7" s="31" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3">
+      <c r="B8" s="31" t="s">
+        <v>456</v>
+      </c>
+      <c r="C8" s="31" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" ht="43.5" customHeight="1">
+      <c r="B9" s="31" t="s">
+        <v>457</v>
+      </c>
+      <c r="C9" s="31" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3">
+      <c r="B10" s="31" t="s">
+        <v>458</v>
+      </c>
+      <c r="C10" s="31" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3">
+      <c r="B11" s="31" t="s">
+        <v>372</v>
+      </c>
+      <c r="C11" s="31" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3">
+      <c r="B12" s="31" t="s">
+        <v>460</v>
+      </c>
+      <c r="C12" s="31" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3">
+      <c r="B13" s="31" t="s">
+        <v>462</v>
+      </c>
+      <c r="C13" s="31" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3">
+      <c r="B14" s="31" t="s">
+        <v>464</v>
+      </c>
+      <c r="C14" s="31" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3">
+      <c r="B15" s="31" t="s">
+        <v>465</v>
+      </c>
+      <c r="C15" s="31" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3">
+      <c r="B16" s="31" t="s">
+        <v>467</v>
+      </c>
+      <c r="C16" s="31" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3">
+      <c r="B17" s="31" t="s">
+        <v>374</v>
+      </c>
+      <c r="C17" s="31" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3">
+      <c r="B18" s="31" t="s">
+        <v>376</v>
+      </c>
+      <c r="C18" s="31" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3">
+      <c r="B19" s="31" t="s">
+        <v>470</v>
+      </c>
+      <c r="C19" s="31" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3">
+      <c r="B20" s="31" t="s">
+        <v>472</v>
+      </c>
+      <c r="C20" s="31" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" ht="29.1" customHeight="1">
+      <c r="B21" s="31" t="s">
+        <v>474</v>
+      </c>
+      <c r="C21" s="31" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3" ht="29.1" customHeight="1">
+      <c r="B22" s="31" t="s">
+        <v>341</v>
+      </c>
+      <c r="C22" s="31" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3" ht="29.1" customHeight="1">
+      <c r="B23" s="31" t="s">
+        <v>447</v>
+      </c>
+      <c r="C23" s="31" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3">
+      <c r="B24" s="31" t="s">
+        <v>478</v>
+      </c>
+      <c r="C24" s="31" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3">
+      <c r="B25" s="31" t="s">
+        <v>480</v>
+      </c>
+      <c r="C25" s="31" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3">
+      <c r="B26" s="31" t="s">
+        <v>482</v>
+      </c>
+      <c r="C26" s="31" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3">
+      <c r="B27" s="31" t="s">
+        <v>398</v>
+      </c>
+      <c r="C27" s="31" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3">
+      <c r="B28" s="31" t="s">
+        <v>342</v>
+      </c>
+      <c r="C28" s="31" t="s">
+        <v>400</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+  <dimension ref="B2:C22"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="27.21875" customWidth="1"/>
+    <col min="3" max="3" width="41.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:3">
+      <c r="B2" s="129" t="s">
+        <v>344</v>
+      </c>
+      <c r="C2" s="129" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3">
+      <c r="B3" s="31" t="s">
+        <v>484</v>
+      </c>
+      <c r="C3" s="31" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3">
+      <c r="B4" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="31" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" ht="43.5" customHeight="1">
+      <c r="B5" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="31" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3">
+      <c r="B6" s="31" t="s">
+        <v>485</v>
+      </c>
+      <c r="C6" s="31" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3">
+      <c r="B7" s="31" t="s">
+        <v>486</v>
+      </c>
+      <c r="C7" s="31" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" ht="29.1" customHeight="1">
+      <c r="B8" s="31" t="s">
+        <v>404</v>
+      </c>
+      <c r="C8" s="31" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3">
+      <c r="B9" s="31" t="s">
+        <v>460</v>
+      </c>
+      <c r="C9" s="31" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3">
+      <c r="B10" s="31" t="s">
+        <v>462</v>
+      </c>
+      <c r="C10" s="31" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3">
+      <c r="B11" s="31" t="s">
+        <v>437</v>
+      </c>
+      <c r="C11" s="31" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3">
+      <c r="B12" s="31" t="s">
+        <v>490</v>
+      </c>
+      <c r="C12" s="31" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3">
+      <c r="B13" s="31" t="s">
+        <v>492</v>
+      </c>
+      <c r="C13" s="31" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3">
+      <c r="B14" s="31" t="s">
+        <v>494</v>
+      </c>
+      <c r="C14" s="31" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3">
+      <c r="B15" s="31" t="s">
+        <v>496</v>
+      </c>
+      <c r="C15" s="31" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3">
+      <c r="B16" s="31" t="s">
+        <v>498</v>
+      </c>
+      <c r="C16" s="31" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3">
+      <c r="B17" s="31" t="s">
+        <v>500</v>
+      </c>
+      <c r="C17" s="31" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3">
+      <c r="B18" s="31" t="s">
+        <v>380</v>
+      </c>
+      <c r="C18" s="31" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3">
+      <c r="B19" s="31" t="s">
+        <v>382</v>
+      </c>
+      <c r="C19" s="31" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3">
+      <c r="B20" s="31" t="s">
+        <v>388</v>
+      </c>
+      <c r="C20" s="31" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3">
+      <c r="B21" s="31" t="s">
+        <v>451</v>
+      </c>
+      <c r="C21" s="31" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3">
+      <c r="B22" s="31" t="s">
+        <v>342</v>
+      </c>
+      <c r="C22" s="31" t="s">
+        <v>453</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="D3:J14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="4" max="4" width="25.81640625" customWidth="1"/>
+    <col min="4" max="4" width="25.77734375" customWidth="1"/>
     <col min="5" max="5" width="32" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.81640625" customWidth="1"/>
-    <col min="7" max="7" width="19.1796875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.77734375" customWidth="1"/>
+    <col min="7" max="7" width="19.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="4:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="4" spans="4:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="D4" s="254" t="s">
+    <row r="3" spans="4:10" ht="15" customHeight="1" thickBot="1"/>
+    <row r="4" spans="4:10" ht="15" customHeight="1" thickBot="1">
+      <c r="D4" s="257" t="s">
         <v>505</v>
       </c>
-      <c r="E4" s="210"/>
-      <c r="F4" s="210"/>
-      <c r="G4" s="208"/>
-    </row>
-    <row r="5" spans="4:10" x14ac:dyDescent="0.35">
-      <c r="D5" s="253" t="s">
+      <c r="E4" s="232"/>
+      <c r="F4" s="232"/>
+      <c r="G4" s="233"/>
+    </row>
+    <row r="5" spans="4:10">
+      <c r="D5" s="266" t="s">
         <v>57</v>
       </c>
-      <c r="E5" s="250" t="s">
+      <c r="E5" s="263" t="s">
         <v>69</v>
       </c>
-      <c r="F5" s="250" t="s">
+      <c r="F5" s="263" t="s">
         <v>506</v>
       </c>
       <c r="G5" s="49" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="6" spans="4:10" x14ac:dyDescent="0.35">
-      <c r="D6" s="220"/>
-      <c r="E6" s="251"/>
-      <c r="F6" s="251"/>
+    <row r="6" spans="4:10">
+      <c r="D6" s="238"/>
+      <c r="E6" s="264"/>
+      <c r="F6" s="264"/>
       <c r="G6" s="51" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="7" spans="4:10" x14ac:dyDescent="0.35">
-      <c r="D7" s="220"/>
-      <c r="E7" s="251"/>
-      <c r="F7" s="251"/>
+    <row r="7" spans="4:10">
+      <c r="D7" s="238"/>
+      <c r="E7" s="264"/>
+      <c r="F7" s="264"/>
       <c r="G7" s="51" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="8" spans="4:10" x14ac:dyDescent="0.35">
-      <c r="D8" s="220"/>
-      <c r="E8" s="251"/>
-      <c r="F8" s="251"/>
+    <row r="8" spans="4:10">
+      <c r="D8" s="238"/>
+      <c r="E8" s="264"/>
+      <c r="F8" s="264"/>
       <c r="G8" s="51" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="9" spans="4:10" x14ac:dyDescent="0.35">
-      <c r="D9" s="220"/>
-      <c r="E9" s="251"/>
-      <c r="F9" s="251"/>
+    <row r="9" spans="4:10">
+      <c r="D9" s="238"/>
+      <c r="E9" s="264"/>
+      <c r="F9" s="264"/>
       <c r="G9" s="51" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="10" spans="4:10" x14ac:dyDescent="0.35">
-      <c r="D10" s="221"/>
-      <c r="E10" s="252"/>
-      <c r="F10" s="252"/>
+    <row r="10" spans="4:10">
+      <c r="D10" s="239"/>
+      <c r="E10" s="265"/>
+      <c r="F10" s="265"/>
       <c r="G10" s="51" t="s">
         <v>511</v>
       </c>
     </row>
-    <row r="11" spans="4:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="4:10" ht="15" customHeight="1" thickBot="1">
       <c r="D11" s="133" t="s">
         <v>512</v>
       </c>
@@ -4482,50 +5577,50 @@
       <c r="F11" s="159"/>
       <c r="G11" s="134"/>
     </row>
-    <row r="12" spans="4:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="4:10">
       <c r="D12" s="48" t="s">
         <v>513</v>
       </c>
       <c r="E12" s="160">
         <v>1</v>
       </c>
-      <c r="F12" s="255" t="s">
+      <c r="F12" s="261" t="s">
         <v>514</v>
       </c>
-      <c r="G12" s="247" t="s">
+      <c r="G12" s="258" t="s">
         <v>515</v>
       </c>
-      <c r="H12" s="247" t="s">
+      <c r="H12" s="258" t="s">
         <v>516</v>
       </c>
-      <c r="I12" s="247" t="s">
+      <c r="I12" s="258" t="s">
         <v>517</v>
       </c>
-      <c r="J12" s="247" t="s">
+      <c r="J12" s="258" t="s">
         <v>518</v>
       </c>
     </row>
-    <row r="13" spans="4:10" x14ac:dyDescent="0.35">
+    <row r="13" spans="4:10">
       <c r="D13" s="50"/>
       <c r="E13" s="112">
         <v>2</v>
       </c>
-      <c r="F13" s="228"/>
-      <c r="G13" s="248"/>
-      <c r="H13" s="248"/>
-      <c r="I13" s="248"/>
-      <c r="J13" s="248"/>
-    </row>
-    <row r="14" spans="4:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="F13" s="244"/>
+      <c r="G13" s="259"/>
+      <c r="H13" s="259"/>
+      <c r="I13" s="259"/>
+      <c r="J13" s="259"/>
+    </row>
+    <row r="14" spans="4:10" ht="15" customHeight="1" thickBot="1">
       <c r="D14" s="52"/>
       <c r="E14" s="113">
         <v>3</v>
       </c>
-      <c r="F14" s="256"/>
-      <c r="G14" s="249"/>
-      <c r="H14" s="249"/>
-      <c r="I14" s="249"/>
-      <c r="J14" s="249"/>
+      <c r="F14" s="262"/>
+      <c r="G14" s="260"/>
+      <c r="H14" s="260"/>
+      <c r="I14" s="260"/>
+      <c r="J14" s="260"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -4543,17 +5638,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="C3:D77"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="3" max="3" width="39.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="39.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="4" spans="3:4" s="162" customFormat="1" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="3:4" ht="15" customHeight="1" thickBot="1"/>
+    <row r="4" spans="3:4" s="162" customFormat="1" ht="16.05" customHeight="1" thickBot="1">
       <c r="C4" s="163" t="s">
         <v>519</v>
       </c>
@@ -4561,7 +5656,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="5" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="3:4">
       <c r="C5" s="164" t="s">
         <v>520</v>
       </c>
@@ -4569,7 +5664,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="6" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="3:4">
       <c r="C6" s="12" t="s">
         <v>522</v>
       </c>
@@ -4577,7 +5672,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="7" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="3:4">
       <c r="C7" s="12" t="s">
         <v>523</v>
       </c>
@@ -4585,7 +5680,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="8" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="3:4">
       <c r="C8" s="12" t="s">
         <v>524</v>
       </c>
@@ -4593,7 +5688,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="9" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="3:4">
       <c r="C9" s="12" t="s">
         <v>525</v>
       </c>
@@ -4601,7 +5696,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="10" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="3:4">
       <c r="C10" s="12" t="s">
         <v>526</v>
       </c>
@@ -4609,7 +5704,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="11" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="3:4">
       <c r="C11" s="77" t="s">
         <v>169</v>
       </c>
@@ -4617,7 +5712,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="12" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="3:4">
       <c r="C12" s="77" t="s">
         <v>175</v>
       </c>
@@ -4625,7 +5720,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="13" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="3:4">
       <c r="C13" s="77" t="s">
         <v>176</v>
       </c>
@@ -4633,7 +5728,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="14" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="3:4">
       <c r="C14" s="77" t="s">
         <v>177</v>
       </c>
@@ -4641,7 +5736,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="15" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="3:4">
       <c r="C15" s="77" t="s">
         <v>178</v>
       </c>
@@ -4649,7 +5744,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="16" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="3:4">
       <c r="C16" s="77" t="s">
         <v>179</v>
       </c>
@@ -4657,7 +5752,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="17" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="3:4">
       <c r="C17" s="77" t="s">
         <v>180</v>
       </c>
@@ -4665,7 +5760,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="18" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="3:4">
       <c r="C18" s="77" t="s">
         <v>181</v>
       </c>
@@ -4673,7 +5768,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="19" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="3:4">
       <c r="C19" s="77" t="s">
         <v>182</v>
       </c>
@@ -4681,7 +5776,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="20" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="3:4">
       <c r="C20" s="77" t="s">
         <v>183</v>
       </c>
@@ -4689,7 +5784,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="21" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="3:4">
       <c r="C21" s="77" t="s">
         <v>184</v>
       </c>
@@ -4697,7 +5792,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="22" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="3:4">
       <c r="C22" s="77" t="s">
         <v>185</v>
       </c>
@@ -4705,7 +5800,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="23" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="3:4">
       <c r="C23" s="77" t="s">
         <v>186</v>
       </c>
@@ -4713,7 +5808,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="24" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="3:4">
       <c r="C24" s="77" t="s">
         <v>187</v>
       </c>
@@ -4721,7 +5816,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="25" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="3:4">
       <c r="C25" s="77" t="s">
         <v>188</v>
       </c>
@@ -4729,7 +5824,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="26" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="3:4">
       <c r="C26" s="77" t="s">
         <v>189</v>
       </c>
@@ -4737,7 +5832,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="27" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="3:4">
       <c r="C27" s="77" t="s">
         <v>190</v>
       </c>
@@ -4745,7 +5840,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="28" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="3:4">
       <c r="C28" s="77" t="s">
         <v>191</v>
       </c>
@@ -4753,7 +5848,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="29" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="29" spans="3:4">
       <c r="C29" s="77" t="s">
         <v>192</v>
       </c>
@@ -4761,7 +5856,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="30" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="30" spans="3:4">
       <c r="C30" s="77" t="s">
         <v>193</v>
       </c>
@@ -4769,7 +5864,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="31" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="3:4">
       <c r="C31" s="77" t="s">
         <v>194</v>
       </c>
@@ -4777,7 +5872,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="32" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="32" spans="3:4">
       <c r="C32" s="77" t="s">
         <v>195</v>
       </c>
@@ -4785,7 +5880,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="33" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="33" spans="3:4">
       <c r="C33" s="77" t="s">
         <v>196</v>
       </c>
@@ -4793,7 +5888,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="34" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="34" spans="3:4">
       <c r="C34" s="77" t="s">
         <v>197</v>
       </c>
@@ -4801,7 +5896,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="35" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="35" spans="3:4">
       <c r="C35" s="77" t="s">
         <v>198</v>
       </c>
@@ -4809,7 +5904,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="36" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="36" spans="3:4">
       <c r="C36" s="77" t="s">
         <v>199</v>
       </c>
@@ -4817,7 +5912,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="37" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="37" spans="3:4">
       <c r="C37" s="77" t="s">
         <v>200</v>
       </c>
@@ -4825,7 +5920,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="38" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="38" spans="3:4">
       <c r="C38" s="77" t="s">
         <v>527</v>
       </c>
@@ -4833,7 +5928,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="39" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="39" spans="3:4">
       <c r="C39" s="77" t="s">
         <v>528</v>
       </c>
@@ -4841,7 +5936,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="40" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="40" spans="3:4">
       <c r="C40" s="77" t="s">
         <v>529</v>
       </c>
@@ -4849,7 +5944,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="41" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="41" spans="3:4">
       <c r="C41" s="77" t="s">
         <v>231</v>
       </c>
@@ -4857,7 +5952,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="42" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="42" spans="3:4">
       <c r="C42" s="77" t="s">
         <v>232</v>
       </c>
@@ -4865,7 +5960,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="43" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="43" spans="3:4">
       <c r="C43" s="77" t="s">
         <v>233</v>
       </c>
@@ -4873,7 +5968,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="44" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="44" spans="3:4">
       <c r="C44" s="77" t="s">
         <v>235</v>
       </c>
@@ -4881,7 +5976,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="45" spans="3:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="3:4" ht="14.55" customHeight="1">
       <c r="C45" s="165" t="s">
         <v>242</v>
       </c>
@@ -4889,7 +5984,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="46" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="46" spans="3:4">
       <c r="C46" s="86" t="s">
         <v>251</v>
       </c>
@@ -4897,7 +5992,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="47" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="47" spans="3:4">
       <c r="C47" s="86" t="s">
         <v>256</v>
       </c>
@@ -4905,7 +6000,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="48" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="48" spans="3:4">
       <c r="C48" s="165" t="s">
         <v>261</v>
       </c>
@@ -4913,7 +6008,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="49" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="49" spans="3:4">
       <c r="C49" s="165" t="s">
         <v>262</v>
       </c>
@@ -4921,7 +6016,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="50" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="50" spans="3:4">
       <c r="C50" s="165" t="s">
         <v>257</v>
       </c>
@@ -4929,7 +6024,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="51" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="51" spans="3:4">
       <c r="C51" s="77" t="s">
         <v>198</v>
       </c>
@@ -4937,7 +6032,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="52" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="52" spans="3:4">
       <c r="C52" s="77" t="s">
         <v>199</v>
       </c>
@@ -4945,7 +6040,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="53" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="53" spans="3:4">
       <c r="C53" s="77" t="s">
         <v>200</v>
       </c>
@@ -4953,7 +6048,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="54" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="54" spans="3:4">
       <c r="C54" s="77" t="s">
         <v>274</v>
       </c>
@@ -4961,7 +6056,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="55" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="55" spans="3:4">
       <c r="C55" s="77" t="s">
         <v>280</v>
       </c>
@@ -4969,7 +6064,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="56" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="56" spans="3:4">
       <c r="C56" s="77" t="s">
         <v>286</v>
       </c>
@@ -4977,7 +6072,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="57" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="57" spans="3:4">
       <c r="C57" s="77" t="s">
         <v>288</v>
       </c>
@@ -4985,7 +6080,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="58" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="58" spans="3:4">
       <c r="C58" s="77" t="s">
         <v>293</v>
       </c>
@@ -4993,7 +6088,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="59" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="59" spans="3:4">
       <c r="C59" s="77" t="s">
         <v>298</v>
       </c>
@@ -5001,7 +6096,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="60" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="60" spans="3:4">
       <c r="C60" s="77" t="s">
         <v>300</v>
       </c>
@@ -5009,7 +6104,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="61" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="61" spans="3:4">
       <c r="C61" s="77" t="s">
         <v>305</v>
       </c>
@@ -5017,7 +6112,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="62" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="62" spans="3:4">
       <c r="C62" s="77" t="s">
         <v>310</v>
       </c>
@@ -5025,7 +6120,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="63" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="63" spans="3:4">
       <c r="C63" s="77" t="s">
         <v>315</v>
       </c>
@@ -5033,7 +6128,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="64" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="64" spans="3:4">
       <c r="C64" s="77" t="s">
         <v>316</v>
       </c>
@@ -5041,7 +6136,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="65" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="65" spans="3:4">
       <c r="C65" s="77" t="s">
         <v>318</v>
       </c>
@@ -5049,7 +6144,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="66" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="66" spans="3:4">
       <c r="C66" s="165" t="s">
         <v>530</v>
       </c>
@@ -5057,7 +6152,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="67" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="67" spans="3:4">
       <c r="C67" s="165" t="s">
         <v>531</v>
       </c>
@@ -5065,7 +6160,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="68" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="68" spans="3:4">
       <c r="C68" s="165" t="s">
         <v>532</v>
       </c>
@@ -5073,7 +6168,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="69" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="69" spans="3:4">
       <c r="C69" s="165" t="s">
         <v>533</v>
       </c>
@@ -5081,7 +6176,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="70" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="70" spans="3:4">
       <c r="C70" s="165" t="s">
         <v>534</v>
       </c>
@@ -5089,7 +6184,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="71" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="71" spans="3:4">
       <c r="C71" s="12" t="s">
         <v>44</v>
       </c>
@@ -5097,7 +6192,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="72" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="72" spans="3:4">
       <c r="C72" s="12" t="s">
         <v>57</v>
       </c>
@@ -5105,7 +6200,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="73" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="73" spans="3:4">
       <c r="C73" s="12" t="s">
         <v>63</v>
       </c>
@@ -5113,7 +6208,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="74" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="74" spans="3:4">
       <c r="C74" s="12" t="s">
         <v>321</v>
       </c>
@@ -5121,7 +6216,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="75" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="75" spans="3:4">
       <c r="C75" s="12" t="s">
         <v>329</v>
       </c>
@@ -5129,7 +6224,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="76" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="76" spans="3:4">
       <c r="C76" s="12" t="s">
         <v>333</v>
       </c>
@@ -5137,115 +6232,12 @@
         <v>521</v>
       </c>
     </row>
-    <row r="77" spans="3:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="3:4" ht="15" customHeight="1" thickBot="1">
       <c r="C77" s="3" t="s">
         <v>338</v>
       </c>
       <c r="D77" s="6" t="s">
         <v>521</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
-  <dimension ref="C3:C13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="3" max="3" width="31.1796875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="3:3" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="4" spans="3:3" x14ac:dyDescent="0.35">
-      <c r="C4" s="132" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="5" spans="3:3" x14ac:dyDescent="0.35">
-      <c r="C5" s="130" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="6" spans="3:3" x14ac:dyDescent="0.35">
-      <c r="C6" s="130" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="7" spans="3:3" x14ac:dyDescent="0.35">
-      <c r="C7" s="130" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="8" spans="3:3" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C8" s="131" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="9" spans="3:3" x14ac:dyDescent="0.35">
-      <c r="C9" s="32"/>
-    </row>
-    <row r="10" spans="3:3" x14ac:dyDescent="0.35">
-      <c r="C10" s="32"/>
-    </row>
-    <row r="11" spans="3:3" x14ac:dyDescent="0.35">
-      <c r="C11" s="32"/>
-    </row>
-    <row r="12" spans="3:3" x14ac:dyDescent="0.35">
-      <c r="C12" s="32"/>
-    </row>
-    <row r="13" spans="3:3" x14ac:dyDescent="0.35">
-      <c r="C13" s="32"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
-  <dimension ref="C3:C10"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="3" max="3" width="31.1796875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="3:3" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="4" spans="3:3" x14ac:dyDescent="0.35">
-      <c r="C4" s="132" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="5" spans="3:3" x14ac:dyDescent="0.35">
-      <c r="C5" s="130" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="6" spans="3:3" x14ac:dyDescent="0.35">
-      <c r="C6" s="130" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="7" spans="3:3" x14ac:dyDescent="0.35">
-      <c r="C7" s="130" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="8" spans="3:3" x14ac:dyDescent="0.35">
-      <c r="C8" s="130" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="9" spans="3:3" x14ac:dyDescent="0.35">
-      <c r="C9" s="130" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="10" spans="3:3" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C10" s="131" t="s">
-        <v>546</v>
       </c>
     </row>
   </sheetData>
@@ -5254,45 +6246,148 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
+  <dimension ref="C3:C13"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="3" max="3" width="31.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="3:3" ht="15" customHeight="1" thickBot="1"/>
+    <row r="4" spans="3:3">
+      <c r="C4" s="132" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="5" spans="3:3">
+      <c r="C5" s="130" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="6" spans="3:3">
+      <c r="C6" s="130" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="7" spans="3:3">
+      <c r="C7" s="130" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="8" spans="3:3" ht="15" customHeight="1" thickBot="1">
+      <c r="C8" s="131" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="9" spans="3:3">
+      <c r="C9" s="32"/>
+    </row>
+    <row r="10" spans="3:3">
+      <c r="C10" s="32"/>
+    </row>
+    <row r="11" spans="3:3">
+      <c r="C11" s="32"/>
+    </row>
+    <row r="12" spans="3:3">
+      <c r="C12" s="32"/>
+    </row>
+    <row r="13" spans="3:3">
+      <c r="C13" s="32"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
+  <dimension ref="C3:C10"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="3" max="3" width="31.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="3:3" ht="15" customHeight="1" thickBot="1"/>
+    <row r="4" spans="3:3">
+      <c r="C4" s="132" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="5" spans="3:3">
+      <c r="C5" s="130" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="6" spans="3:3">
+      <c r="C6" s="130" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="7" spans="3:3">
+      <c r="C7" s="130" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="8" spans="3:3">
+      <c r="C8" s="130" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="9" spans="3:3">
+      <c r="C9" s="130" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="10" spans="3:3" ht="15" customHeight="1" thickBot="1">
+      <c r="C10" s="131" t="s">
+        <v>546</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="D6:J18"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="4" width="9.1796875" style="27" customWidth="1"/>
-    <col min="5" max="5" width="16.7265625" style="27" customWidth="1"/>
-    <col min="6" max="6" width="18.453125" style="27" customWidth="1"/>
-    <col min="7" max="7" width="9.1796875" style="27" customWidth="1"/>
-    <col min="8" max="16384" width="9.1796875" style="27"/>
+    <col min="1" max="4" width="9.21875" style="27" customWidth="1"/>
+    <col min="5" max="5" width="16.77734375" style="27" customWidth="1"/>
+    <col min="6" max="6" width="18.44140625" style="27" customWidth="1"/>
+    <col min="7" max="7" width="9.21875" style="27" customWidth="1"/>
+    <col min="8" max="16384" width="9.21875" style="27"/>
   </cols>
   <sheetData>
-    <row r="6" spans="4:10" ht="36" customHeight="1" x14ac:dyDescent="0.8">
+    <row r="6" spans="4:10" ht="36" customHeight="1">
       <c r="D6" s="28" t="s">
         <v>547</v>
       </c>
     </row>
-    <row r="10" spans="4:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="4:10">
       <c r="H10" s="114" t="s">
         <v>548</v>
       </c>
       <c r="I10" s="114"/>
       <c r="J10" s="114"/>
     </row>
-    <row r="11" spans="4:10" x14ac:dyDescent="0.35">
+    <row r="11" spans="4:10">
       <c r="H11" s="27" t="s">
         <v>549</v>
       </c>
     </row>
-    <row r="12" spans="4:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="4:10">
       <c r="H12" s="27" t="s">
         <v>550</v>
       </c>
     </row>
-    <row r="13" spans="4:10" x14ac:dyDescent="0.35">
+    <row r="13" spans="4:10">
       <c r="H13" s="27" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="14" spans="4:10" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="4:10" ht="27" customHeight="1">
       <c r="E14" s="29" t="s">
         <v>551</v>
       </c>
@@ -5301,7 +6396,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="15" spans="4:10" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="4:10" ht="27" customHeight="1">
       <c r="E15" s="29" t="s">
         <v>553</v>
       </c>
@@ -5310,12 +6405,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="16" spans="4:10" x14ac:dyDescent="0.35">
+    <row r="16" spans="4:10">
       <c r="H16" s="27" t="s">
         <v>554</v>
       </c>
     </row>
-    <row r="18" spans="8:8" x14ac:dyDescent="0.35">
+    <row r="18" spans="8:8">
       <c r="H18" s="27" t="s">
         <v>555</v>
       </c>
@@ -5326,17 +6421,1414 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E9FF2DD-8784-49B6-9467-1786ED6D06B3}">
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:C150"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="107.109375" style="267" customWidth="1"/>
+    <col min="3" max="3" width="19.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>583</v>
+      </c>
+      <c r="B1" s="267" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="28.8" hidden="1">
+      <c r="A2" t="s">
+        <v>584</v>
+      </c>
+      <c r="B2" s="267" t="s">
+        <v>585</v>
+      </c>
+      <c r="C2" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" hidden="1">
+      <c r="A3" t="s">
+        <v>587</v>
+      </c>
+      <c r="B3" s="267" t="s">
+        <v>588</v>
+      </c>
+      <c r="C3" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" hidden="1">
+      <c r="A4" t="s">
+        <v>590</v>
+      </c>
+      <c r="B4" s="267" t="s">
+        <v>591</v>
+      </c>
+      <c r="C4" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" hidden="1">
+      <c r="A5" t="s">
+        <v>590</v>
+      </c>
+      <c r="B5" s="267" t="s">
+        <v>592</v>
+      </c>
+      <c r="C5" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" hidden="1">
+      <c r="A6" t="s">
+        <v>590</v>
+      </c>
+      <c r="B6" s="267" t="s">
+        <v>593</v>
+      </c>
+      <c r="C6" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" hidden="1">
+      <c r="A7" t="s">
+        <v>590</v>
+      </c>
+      <c r="B7" s="267" t="s">
+        <v>594</v>
+      </c>
+      <c r="C7" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" hidden="1">
+      <c r="A8" t="s">
+        <v>590</v>
+      </c>
+      <c r="B8" s="267" t="s">
+        <v>595</v>
+      </c>
+      <c r="C8" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" hidden="1">
+      <c r="A9" t="s">
+        <v>590</v>
+      </c>
+      <c r="B9" s="267" t="s">
+        <v>596</v>
+      </c>
+      <c r="C9" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="28.8" hidden="1">
+      <c r="A10" t="s">
+        <v>590</v>
+      </c>
+      <c r="B10" s="267" t="s">
+        <v>597</v>
+      </c>
+      <c r="C10" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" hidden="1">
+      <c r="A11" t="s">
+        <v>590</v>
+      </c>
+      <c r="B11" s="267" t="s">
+        <v>598</v>
+      </c>
+      <c r="C11" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" hidden="1">
+      <c r="A12" t="s">
+        <v>590</v>
+      </c>
+      <c r="B12" s="267" t="s">
+        <v>599</v>
+      </c>
+      <c r="C12" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" hidden="1">
+      <c r="A13" t="s">
+        <v>600</v>
+      </c>
+      <c r="B13" s="267" t="s">
+        <v>601</v>
+      </c>
+      <c r="C13" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" hidden="1">
+      <c r="A14" t="s">
+        <v>590</v>
+      </c>
+      <c r="B14" s="267" t="s">
+        <v>602</v>
+      </c>
+      <c r="C14" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" hidden="1">
+      <c r="A15" t="s">
+        <v>590</v>
+      </c>
+      <c r="B15" s="267" t="s">
+        <v>603</v>
+      </c>
+      <c r="C15" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" hidden="1">
+      <c r="A16" t="s">
+        <v>604</v>
+      </c>
+      <c r="B16" s="267" t="s">
+        <v>605</v>
+      </c>
+      <c r="C16" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" hidden="1">
+      <c r="A17" t="s">
+        <v>587</v>
+      </c>
+      <c r="B17" s="267" t="s">
+        <v>606</v>
+      </c>
+      <c r="C17" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" hidden="1">
+      <c r="A18" t="s">
+        <v>604</v>
+      </c>
+      <c r="B18" s="267" t="s">
+        <v>607</v>
+      </c>
+      <c r="C18" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" hidden="1">
+      <c r="A19" t="s">
+        <v>608</v>
+      </c>
+      <c r="B19" s="267" t="s">
+        <v>609</v>
+      </c>
+      <c r="C19" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" hidden="1">
+      <c r="A20" t="s">
+        <v>587</v>
+      </c>
+      <c r="B20" s="267" t="s">
+        <v>610</v>
+      </c>
+      <c r="C20" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="28.8" hidden="1">
+      <c r="A21" t="s">
+        <v>590</v>
+      </c>
+      <c r="B21" s="267" t="s">
+        <v>611</v>
+      </c>
+      <c r="C21" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" hidden="1">
+      <c r="A22" t="s">
+        <v>587</v>
+      </c>
+      <c r="B22" s="267" t="s">
+        <v>613</v>
+      </c>
+      <c r="C22" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" hidden="1">
+      <c r="A23" t="s">
+        <v>614</v>
+      </c>
+      <c r="B23" s="267" t="s">
+        <v>615</v>
+      </c>
+      <c r="C23" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" hidden="1">
+      <c r="A24" t="s">
+        <v>604</v>
+      </c>
+      <c r="B24" s="267" t="s">
+        <v>616</v>
+      </c>
+      <c r="C24" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" hidden="1">
+      <c r="A25" t="s">
+        <v>617</v>
+      </c>
+      <c r="B25" s="267" t="s">
+        <v>618</v>
+      </c>
+      <c r="C25" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" hidden="1">
+      <c r="A26" t="s">
+        <v>619</v>
+      </c>
+      <c r="B26" s="267" t="s">
+        <v>620</v>
+      </c>
+      <c r="C26" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" hidden="1">
+      <c r="A27" t="s">
+        <v>587</v>
+      </c>
+      <c r="B27" s="267" t="s">
+        <v>621</v>
+      </c>
+      <c r="C27" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" hidden="1">
+      <c r="A28" t="s">
+        <v>587</v>
+      </c>
+      <c r="B28" s="267" t="s">
+        <v>622</v>
+      </c>
+      <c r="C28" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="28.8" hidden="1">
+      <c r="A29" t="s">
+        <v>623</v>
+      </c>
+      <c r="B29" s="267" t="s">
+        <v>624</v>
+      </c>
+      <c r="C29" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" hidden="1">
+      <c r="A30" t="s">
+        <v>600</v>
+      </c>
+      <c r="B30" s="267" t="s">
+        <v>625</v>
+      </c>
+      <c r="C30" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" hidden="1">
+      <c r="A31" t="s">
+        <v>600</v>
+      </c>
+      <c r="B31" s="267" t="s">
+        <v>626</v>
+      </c>
+      <c r="C31" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" hidden="1">
+      <c r="A32" t="s">
+        <v>590</v>
+      </c>
+      <c r="B32" s="267" t="s">
+        <v>627</v>
+      </c>
+      <c r="C32" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" hidden="1">
+      <c r="A33" t="s">
+        <v>587</v>
+      </c>
+      <c r="B33" s="267" t="s">
+        <v>628</v>
+      </c>
+      <c r="C33" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="43.2" hidden="1" customHeight="1">
+      <c r="A34" t="s">
+        <v>629</v>
+      </c>
+      <c r="B34" s="267" t="s">
+        <v>630</v>
+      </c>
+      <c r="C34" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" hidden="1">
+      <c r="A35" t="s">
+        <v>619</v>
+      </c>
+      <c r="B35" s="267" t="s">
+        <v>631</v>
+      </c>
+      <c r="C35" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" hidden="1">
+      <c r="A36" t="s">
+        <v>632</v>
+      </c>
+      <c r="B36" s="267" t="s">
+        <v>633</v>
+      </c>
+      <c r="C36" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" hidden="1">
+      <c r="A37" t="s">
+        <v>587</v>
+      </c>
+      <c r="B37" s="267" t="s">
+        <v>634</v>
+      </c>
+      <c r="C37" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" hidden="1">
+      <c r="A38" t="s">
+        <v>635</v>
+      </c>
+      <c r="B38" s="267" t="s">
+        <v>636</v>
+      </c>
+      <c r="C38" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" hidden="1">
+      <c r="A39" t="s">
+        <v>637</v>
+      </c>
+      <c r="B39" s="267" t="s">
+        <v>638</v>
+      </c>
+      <c r="C39" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" hidden="1">
+      <c r="A40" t="s">
+        <v>639</v>
+      </c>
+      <c r="B40" s="267" t="s">
+        <v>640</v>
+      </c>
+      <c r="C40" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" hidden="1">
+      <c r="A41" t="s">
+        <v>629</v>
+      </c>
+      <c r="B41" s="267" t="s">
+        <v>641</v>
+      </c>
+      <c r="C41" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" hidden="1">
+      <c r="A42" t="s">
+        <v>642</v>
+      </c>
+      <c r="B42" s="267" t="s">
+        <v>643</v>
+      </c>
+      <c r="C42" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" hidden="1">
+      <c r="A43" t="s">
+        <v>644</v>
+      </c>
+      <c r="B43" s="267" t="s">
+        <v>645</v>
+      </c>
+      <c r="C43" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" hidden="1">
+      <c r="A44" t="s">
+        <v>646</v>
+      </c>
+      <c r="B44" s="267" t="s">
+        <v>647</v>
+      </c>
+      <c r="C44" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" hidden="1">
+      <c r="A45" t="s">
+        <v>584</v>
+      </c>
+      <c r="B45" s="267" t="s">
+        <v>648</v>
+      </c>
+      <c r="C45" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" hidden="1">
+      <c r="A46" t="s">
+        <v>590</v>
+      </c>
+      <c r="B46" s="267" t="s">
+        <v>649</v>
+      </c>
+      <c r="C46" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" hidden="1">
+      <c r="A47" t="s">
+        <v>646</v>
+      </c>
+      <c r="B47" s="267" t="s">
+        <v>650</v>
+      </c>
+      <c r="C47" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" hidden="1">
+      <c r="A48" t="s">
+        <v>604</v>
+      </c>
+      <c r="B48" s="267" t="s">
+        <v>651</v>
+      </c>
+      <c r="C48" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" hidden="1">
+      <c r="A49" t="s">
+        <v>614</v>
+      </c>
+      <c r="B49" s="267" t="s">
+        <v>652</v>
+      </c>
+      <c r="C49" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" hidden="1">
+      <c r="A50" t="s">
+        <v>653</v>
+      </c>
+      <c r="B50" s="267" t="s">
+        <v>654</v>
+      </c>
+      <c r="C50" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" hidden="1">
+      <c r="A51" t="s">
+        <v>623</v>
+      </c>
+      <c r="B51" s="267" t="s">
+        <v>656</v>
+      </c>
+      <c r="C51" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" hidden="1">
+      <c r="A52" t="s">
+        <v>623</v>
+      </c>
+      <c r="B52" s="267" t="s">
+        <v>657</v>
+      </c>
+      <c r="C52" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" hidden="1">
+      <c r="A53" t="s">
+        <v>658</v>
+      </c>
+      <c r="B53" s="267" t="s">
+        <v>659</v>
+      </c>
+      <c r="C53" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" hidden="1">
+      <c r="A54" t="s">
+        <v>619</v>
+      </c>
+      <c r="B54" s="268" t="s">
+        <v>660</v>
+      </c>
+      <c r="C54" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" hidden="1">
+      <c r="A55" t="s">
+        <v>619</v>
+      </c>
+      <c r="B55" s="267" t="s">
+        <v>661</v>
+      </c>
+      <c r="C55" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" hidden="1">
+      <c r="A56" t="s">
+        <v>662</v>
+      </c>
+      <c r="B56" s="267" t="s">
+        <v>663</v>
+      </c>
+      <c r="C56" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" hidden="1">
+      <c r="A57" t="s">
+        <v>617</v>
+      </c>
+      <c r="B57" s="267" t="s">
+        <v>664</v>
+      </c>
+      <c r="C57" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" ht="86.4" hidden="1">
+      <c r="B58" s="267" t="s">
+        <v>665</v>
+      </c>
+      <c r="C58" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" ht="100.8" hidden="1">
+      <c r="B59" s="267" t="s">
+        <v>666</v>
+      </c>
+      <c r="C59" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" hidden="1">
+      <c r="B60" s="267" t="s">
+        <v>667</v>
+      </c>
+      <c r="C60" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" hidden="1">
+      <c r="B61" s="267" t="s">
+        <v>668</v>
+      </c>
+      <c r="C61" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" hidden="1">
+      <c r="B62" s="267" t="s">
+        <v>669</v>
+      </c>
+      <c r="C62" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" hidden="1">
+      <c r="B63" s="267" t="s">
+        <v>670</v>
+      </c>
+      <c r="C63" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" hidden="1">
+      <c r="B64" s="267" t="s">
+        <v>671</v>
+      </c>
+      <c r="C64" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="65" spans="2:3" hidden="1">
+      <c r="B65" s="267" t="s">
+        <v>672</v>
+      </c>
+      <c r="C65" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="66" spans="2:3" hidden="1">
+      <c r="B66" s="267" t="s">
+        <v>673</v>
+      </c>
+      <c r="C66" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="67" spans="2:3" hidden="1">
+      <c r="B67" s="267" t="s">
+        <v>674</v>
+      </c>
+      <c r="C67" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="68" spans="2:3" hidden="1">
+      <c r="B68" s="267" t="s">
+        <v>675</v>
+      </c>
+      <c r="C68" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="69" spans="2:3" hidden="1">
+      <c r="B69" s="267" t="s">
+        <v>676</v>
+      </c>
+      <c r="C69" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="70" spans="2:3" hidden="1">
+      <c r="B70" s="267" t="s">
+        <v>677</v>
+      </c>
+      <c r="C70" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="71" spans="2:3" hidden="1">
+      <c r="B71" s="267" t="s">
+        <v>678</v>
+      </c>
+      <c r="C71" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="72" spans="2:3" hidden="1">
+      <c r="B72" s="267" t="s">
+        <v>679</v>
+      </c>
+      <c r="C72" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="73" spans="2:3" hidden="1">
+      <c r="B73" s="267" t="s">
+        <v>680</v>
+      </c>
+      <c r="C73" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="74" spans="2:3" hidden="1">
+      <c r="B74" s="267" t="s">
+        <v>681</v>
+      </c>
+      <c r="C74" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="75" spans="2:3" hidden="1">
+      <c r="B75" s="267" t="s">
+        <v>682</v>
+      </c>
+      <c r="C75" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="76" spans="2:3" hidden="1">
+      <c r="B76" s="267" t="s">
+        <v>683</v>
+      </c>
+      <c r="C76" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="77" spans="2:3" hidden="1">
+      <c r="B77" s="267" t="s">
+        <v>684</v>
+      </c>
+      <c r="C77" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="78" spans="2:3" hidden="1">
+      <c r="B78" s="267" t="s">
+        <v>685</v>
+      </c>
+      <c r="C78" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="79" spans="2:3" hidden="1">
+      <c r="B79" s="267" t="s">
+        <v>686</v>
+      </c>
+      <c r="C79" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="80" spans="2:3" ht="28.8" hidden="1">
+      <c r="B80" s="267" t="s">
+        <v>687</v>
+      </c>
+      <c r="C80" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="81" spans="2:3" hidden="1">
+      <c r="B81" s="267" t="s">
+        <v>688</v>
+      </c>
+      <c r="C81" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="82" spans="2:3" hidden="1">
+      <c r="B82" s="267" t="s">
+        <v>689</v>
+      </c>
+      <c r="C82" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="83" spans="2:3" hidden="1">
+      <c r="B83" s="267" t="s">
+        <v>690</v>
+      </c>
+      <c r="C83" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="84" spans="2:3" hidden="1">
+      <c r="B84" s="267" t="s">
+        <v>691</v>
+      </c>
+      <c r="C84" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="85" spans="2:3" hidden="1">
+      <c r="B85" s="267" t="s">
+        <v>692</v>
+      </c>
+      <c r="C85" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="86" spans="2:3" hidden="1">
+      <c r="B86" s="267" t="s">
+        <v>693</v>
+      </c>
+      <c r="C86" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="87" spans="2:3" hidden="1">
+      <c r="B87" s="267" t="s">
+        <v>694</v>
+      </c>
+      <c r="C87" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="88" spans="2:3" ht="28.8" hidden="1">
+      <c r="B88" s="267" t="s">
+        <v>695</v>
+      </c>
+      <c r="C88" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="89" spans="2:3" hidden="1">
+      <c r="B89" s="267" t="s">
+        <v>696</v>
+      </c>
+      <c r="C89" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="90" spans="2:3" ht="28.8" hidden="1">
+      <c r="B90" s="267" t="s">
+        <v>697</v>
+      </c>
+      <c r="C90" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="91" spans="2:3" hidden="1">
+      <c r="B91" s="267" t="s">
+        <v>698</v>
+      </c>
+      <c r="C91" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="92" spans="2:3" hidden="1">
+      <c r="B92" s="267" t="s">
+        <v>699</v>
+      </c>
+      <c r="C92" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="93" spans="2:3" hidden="1">
+      <c r="B93" s="267" t="s">
+        <v>700</v>
+      </c>
+      <c r="C93" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="94" spans="2:3" hidden="1">
+      <c r="B94" s="267" t="s">
+        <v>701</v>
+      </c>
+      <c r="C94" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="95" spans="2:3" hidden="1">
+      <c r="B95" s="267" t="s">
+        <v>702</v>
+      </c>
+      <c r="C95" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="96" spans="2:3" hidden="1">
+      <c r="B96" s="269" t="s">
+        <v>703</v>
+      </c>
+      <c r="C96" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="97" spans="2:3" hidden="1">
+      <c r="B97" s="267" t="s">
+        <v>704</v>
+      </c>
+      <c r="C97" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="98" spans="2:3" hidden="1">
+      <c r="B98" s="267" t="s">
+        <v>705</v>
+      </c>
+      <c r="C98" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="99" spans="2:3" hidden="1">
+      <c r="B99" s="267" t="s">
+        <v>706</v>
+      </c>
+      <c r="C99" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="100" spans="2:3" hidden="1">
+      <c r="B100" s="267" t="s">
+        <v>707</v>
+      </c>
+      <c r="C100" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="101" spans="2:3" hidden="1">
+      <c r="B101" s="267" t="s">
+        <v>709</v>
+      </c>
+      <c r="C101" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="102" spans="2:3" ht="28.8" hidden="1">
+      <c r="B102" s="267" t="s">
+        <v>710</v>
+      </c>
+      <c r="C102" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="103" spans="2:3" hidden="1">
+      <c r="B103" s="267" t="s">
+        <v>711</v>
+      </c>
+      <c r="C103" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="104" spans="2:3" hidden="1">
+      <c r="B104" s="267" t="s">
+        <v>712</v>
+      </c>
+      <c r="C104" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="105" spans="2:3" hidden="1">
+      <c r="B105" s="267" t="s">
+        <v>713</v>
+      </c>
+      <c r="C105" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="106" spans="2:3" hidden="1">
+      <c r="B106" s="267" t="s">
+        <v>714</v>
+      </c>
+      <c r="C106" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="107" spans="2:3" hidden="1">
+      <c r="B107" s="267" t="s">
+        <v>715</v>
+      </c>
+      <c r="C107" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="108" spans="2:3" hidden="1">
+      <c r="B108" s="267" t="s">
+        <v>716</v>
+      </c>
+      <c r="C108" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="109" spans="2:3" hidden="1">
+      <c r="B109" s="267" t="s">
+        <v>717</v>
+      </c>
+      <c r="C109" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="110" spans="2:3" hidden="1">
+      <c r="B110" s="267" t="s">
+        <v>718</v>
+      </c>
+      <c r="C110" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="111" spans="2:3" hidden="1">
+      <c r="B111" s="267" t="s">
+        <v>719</v>
+      </c>
+      <c r="C111" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="112" spans="2:3" hidden="1">
+      <c r="B112" s="267" t="s">
+        <v>720</v>
+      </c>
+      <c r="C112" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="113" spans="2:3" hidden="1">
+      <c r="B113" s="267" t="s">
+        <v>721</v>
+      </c>
+      <c r="C113" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="114" spans="2:3" hidden="1">
+      <c r="B114" s="267" t="s">
+        <v>722</v>
+      </c>
+      <c r="C114" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="115" spans="2:3" hidden="1">
+      <c r="B115" s="267" t="s">
+        <v>723</v>
+      </c>
+      <c r="C115" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="116" spans="2:3" hidden="1">
+      <c r="B116" s="267" t="s">
+        <v>724</v>
+      </c>
+      <c r="C116" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="117" spans="2:3" hidden="1">
+      <c r="B117" s="267" t="s">
+        <v>725</v>
+      </c>
+      <c r="C117" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="118" spans="2:3" hidden="1">
+      <c r="B118" s="267" t="s">
+        <v>726</v>
+      </c>
+      <c r="C118" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="119" spans="2:3" hidden="1">
+      <c r="B119" s="267" t="s">
+        <v>727</v>
+      </c>
+      <c r="C119" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="120" spans="2:3" hidden="1">
+      <c r="B120" s="267" t="s">
+        <v>728</v>
+      </c>
+      <c r="C120" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="121" spans="2:3" hidden="1">
+      <c r="B121" s="267" t="s">
+        <v>729</v>
+      </c>
+      <c r="C121" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="122" spans="2:3" hidden="1">
+      <c r="B122" s="267" t="s">
+        <v>730</v>
+      </c>
+      <c r="C122" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="123" spans="2:3" hidden="1">
+      <c r="B123" s="267" t="s">
+        <v>731</v>
+      </c>
+      <c r="C123" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="124" spans="2:3" hidden="1">
+      <c r="B124" s="267" t="s">
+        <v>732</v>
+      </c>
+      <c r="C124" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="125" spans="2:3" hidden="1">
+      <c r="B125" s="267" t="s">
+        <v>733</v>
+      </c>
+      <c r="C125" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="126" spans="2:3" hidden="1">
+      <c r="B126" s="267" t="s">
+        <v>734</v>
+      </c>
+      <c r="C126" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="127" spans="2:3" hidden="1">
+      <c r="B127" s="267" t="s">
+        <v>735</v>
+      </c>
+      <c r="C127" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="128" spans="2:3" hidden="1">
+      <c r="B128" s="267" t="s">
+        <v>736</v>
+      </c>
+      <c r="C128" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="129" spans="2:3" hidden="1">
+      <c r="B129" s="267" t="s">
+        <v>737</v>
+      </c>
+      <c r="C129" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="130" spans="2:3" hidden="1">
+      <c r="B130" s="267" t="s">
+        <v>738</v>
+      </c>
+      <c r="C130" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="131" spans="2:3" hidden="1">
+      <c r="B131" s="267" t="s">
+        <v>739</v>
+      </c>
+      <c r="C131" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="132" spans="2:3" hidden="1">
+      <c r="B132" s="267" t="s">
+        <v>740</v>
+      </c>
+      <c r="C132" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="133" spans="2:3" hidden="1">
+      <c r="B133" s="267" t="s">
+        <v>741</v>
+      </c>
+      <c r="C133" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="134" spans="2:3" hidden="1">
+      <c r="B134" s="267" t="s">
+        <v>742</v>
+      </c>
+      <c r="C134" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="135" spans="2:3" hidden="1">
+      <c r="B135" s="267" t="s">
+        <v>743</v>
+      </c>
+      <c r="C135" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="136" spans="2:3" hidden="1">
+      <c r="B136" s="267" t="s">
+        <v>744</v>
+      </c>
+      <c r="C136" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="137" spans="2:3" ht="28.8" hidden="1">
+      <c r="B137" s="267" t="s">
+        <v>745</v>
+      </c>
+      <c r="C137" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="138" spans="2:3" hidden="1">
+      <c r="B138" s="267" t="s">
+        <v>746</v>
+      </c>
+      <c r="C138" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="139" spans="2:3" ht="28.8" hidden="1">
+      <c r="B139" s="267" t="s">
+        <v>747</v>
+      </c>
+      <c r="C139" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="140" spans="2:3" ht="28.8" hidden="1">
+      <c r="B140" s="267" t="s">
+        <v>748</v>
+      </c>
+      <c r="C140" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="141" spans="2:3" hidden="1">
+      <c r="B141" s="267" t="s">
+        <v>749</v>
+      </c>
+      <c r="C141" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="142" spans="2:3" ht="28.8">
+      <c r="B142" s="267" t="s">
+        <v>750</v>
+      </c>
+      <c r="C142" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="143" spans="2:3" hidden="1">
+      <c r="B143" s="267" t="s">
+        <v>752</v>
+      </c>
+      <c r="C143" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="144" spans="2:3" ht="28.8" hidden="1">
+      <c r="B144" s="267" t="s">
+        <v>753</v>
+      </c>
+      <c r="C144" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="145" spans="2:3" ht="28.8" hidden="1">
+      <c r="B145" s="267" t="s">
+        <v>754</v>
+      </c>
+      <c r="C145" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="146" spans="2:3" hidden="1">
+      <c r="B146" s="267" t="s">
+        <v>755</v>
+      </c>
+      <c r="C146" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="147" spans="2:3">
+      <c r="B147" s="267" t="s">
+        <v>756</v>
+      </c>
+      <c r="C147" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="148" spans="2:3">
+      <c r="B148" s="267" t="s">
+        <v>757</v>
+      </c>
+      <c r="C148" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="149" spans="2:3">
+      <c r="B149" s="267" t="s">
+        <v>758</v>
+      </c>
+      <c r="C149" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="150" spans="2:3">
+      <c r="B150" s="267" t="s">
+        <v>759</v>
+      </c>
+      <c r="C150" t="s">
+        <v>751</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C146" xr:uid="{5A64B360-020C-4527-96C0-33FA20016D59}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="Pending"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <hyperlinks>
+    <hyperlink ref="B96" r:id="rId1" xr:uid="{3461AE56-71F3-4FE7-A3DC-D4A934254BE8}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="B2:D11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="3" max="3" width="64.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="64.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="3" spans="2:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:4" ht="15" customHeight="1" thickBot="1"/>
+    <row r="3" spans="2:4" ht="15" customHeight="1" thickBot="1">
       <c r="B3" s="104" t="s">
         <v>556</v>
       </c>
@@ -5347,7 +7839,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:4">
       <c r="B4" s="101">
         <v>1</v>
       </c>
@@ -5358,7 +7850,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:4">
       <c r="B5" s="102">
         <v>2</v>
       </c>
@@ -5369,7 +7861,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:4">
       <c r="B6" s="102">
         <v>3</v>
       </c>
@@ -5380,7 +7872,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:4">
       <c r="B7" s="102">
         <v>4</v>
       </c>
@@ -5391,7 +7883,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:4">
       <c r="B8" s="102">
         <v>5</v>
       </c>
@@ -5402,7 +7894,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:4">
       <c r="B9" s="102">
         <v>6</v>
       </c>
@@ -5413,7 +7905,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:4">
       <c r="B10" s="168">
         <v>7</v>
       </c>
@@ -5424,7 +7916,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="11" spans="2:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:4" ht="15" customHeight="1" thickBot="1">
       <c r="B11" s="103">
         <v>8</v>
       </c>
@@ -5456,19 +7948,19 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="B2:F7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="3" max="3" width="37.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.26953125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="65.1796875" customWidth="1"/>
-    <col min="6" max="6" width="14.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="65.21875" customWidth="1"/>
+    <col min="6" max="6" width="14.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="3" spans="2:6" s="26" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:6" ht="15" customHeight="1" thickBot="1"/>
+    <row r="3" spans="2:6" s="26" customFormat="1" ht="15" customHeight="1" thickBot="1">
       <c r="B3" s="178" t="s">
         <v>568</v>
       </c>
@@ -5485,7 +7977,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="4" spans="2:6" ht="87.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:6" ht="87.6" customHeight="1" thickBot="1">
       <c r="B4" s="179">
         <v>1</v>
       </c>
@@ -5502,7 +7994,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="5" spans="2:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:6" ht="15" customHeight="1" thickBot="1">
       <c r="B5" s="152">
         <v>2</v>
       </c>
@@ -5519,7 +8011,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="6" spans="2:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:6" ht="15" customHeight="1" thickBot="1">
       <c r="B6" s="180">
         <v>3</v>
       </c>
@@ -5536,7 +8028,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:6">
       <c r="B7" s="174">
         <v>4</v>
       </c>
@@ -5549,20 +8041,59 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEAE253A-ADFE-437B-AFC0-C5CC1F828D7F}">
+  <dimension ref="B1:C3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="13.21875" customWidth="1"/>
+    <col min="2" max="2" width="67.77734375" customWidth="1"/>
+    <col min="3" max="3" width="15.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:3">
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="2" spans="2:3">
+      <c r="B2" t="s">
+        <v>760</v>
+      </c>
+      <c r="C2" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3" ht="28.8">
+      <c r="B3" s="267" t="s">
+        <v>761</v>
+      </c>
+      <c r="C3" t="s">
+        <v>751</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B4:C11"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.1796875" style="27" customWidth="1"/>
-    <col min="2" max="2" width="34.81640625" style="27" customWidth="1"/>
+    <col min="1" max="1" width="9.21875" style="27" customWidth="1"/>
+    <col min="2" max="2" width="34.77734375" style="27" customWidth="1"/>
     <col min="3" max="3" width="67" style="27" customWidth="1"/>
-    <col min="4" max="4" width="9.1796875" style="27" customWidth="1"/>
-    <col min="5" max="16384" width="9.1796875" style="27"/>
+    <col min="4" max="4" width="9.21875" style="27" customWidth="1"/>
+    <col min="5" max="16384" width="9.21875" style="27"/>
   </cols>
   <sheetData>
-    <row r="4" spans="2:3" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="5" spans="2:3" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:3" ht="15" customHeight="1" thickBot="1"/>
+    <row r="5" spans="2:3" ht="15" customHeight="1" thickBot="1">
       <c r="B5" s="107" t="s">
         <v>0</v>
       </c>
@@ -5570,7 +8101,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="2:3" ht="29.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:3" ht="29.1" customHeight="1">
       <c r="B6" s="62" t="s">
         <v>2</v>
       </c>
@@ -5578,7 +8109,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="2:3" ht="29.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:3" ht="29.1" customHeight="1">
       <c r="B7" s="58" t="s">
         <v>4</v>
       </c>
@@ -5586,7 +8117,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:3">
       <c r="B8" s="58" t="s">
         <v>6</v>
       </c>
@@ -5594,7 +8125,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="2:3" ht="29.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:3" ht="29.1" customHeight="1">
       <c r="B9" s="60" t="s">
         <v>8</v>
       </c>
@@ -5602,7 +8133,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="2:3" ht="29.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:3" ht="29.1" customHeight="1">
       <c r="B10" s="60" t="s">
         <v>10</v>
       </c>
@@ -5610,7 +8141,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="2:3" ht="29.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:3" ht="29.55" customHeight="1" thickBot="1">
       <c r="B11" s="61" t="s">
         <v>12</v>
       </c>
@@ -5624,79 +8155,79 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="C2:D13"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="18.5" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="3" width="9.1796875" style="110" customWidth="1"/>
-    <col min="4" max="4" width="62.81640625" style="110" customWidth="1"/>
-    <col min="5" max="5" width="9.1796875" style="110" customWidth="1"/>
-    <col min="6" max="16384" width="9.1796875" style="110"/>
+    <col min="1" max="3" width="9.21875" style="110" customWidth="1"/>
+    <col min="4" max="4" width="62.77734375" style="110" customWidth="1"/>
+    <col min="5" max="5" width="9.21875" style="110" customWidth="1"/>
+    <col min="6" max="16384" width="9.21875" style="110"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="3" spans="3:4" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="C3" s="207" t="s">
+    <row r="2" spans="3:4" ht="19.05" customHeight="1" thickBot="1"/>
+    <row r="3" spans="3:4" ht="19.05" customHeight="1" thickBot="1">
+      <c r="C3" s="252" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="208"/>
-    </row>
-    <row r="4" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="D3" s="233"/>
+    </row>
+    <row r="4" spans="3:4">
       <c r="C4" s="111" t="s">
         <v>15</v>
       </c>
       <c r="D4" s="111"/>
     </row>
-    <row r="5" spans="3:4" x14ac:dyDescent="0.45">
+    <row r="5" spans="3:4">
       <c r="C5" s="109" t="s">
         <v>16</v>
       </c>
       <c r="D5" s="109"/>
     </row>
-    <row r="6" spans="3:4" x14ac:dyDescent="0.45">
+    <row r="6" spans="3:4">
       <c r="C6" s="109" t="s">
         <v>17</v>
       </c>
       <c r="D6" s="109"/>
     </row>
-    <row r="7" spans="3:4" x14ac:dyDescent="0.45">
+    <row r="7" spans="3:4">
       <c r="C7" s="109" t="s">
         <v>18</v>
       </c>
       <c r="D7" s="109"/>
     </row>
-    <row r="8" spans="3:4" x14ac:dyDescent="0.45">
+    <row r="8" spans="3:4">
       <c r="C8" s="109" t="s">
         <v>19</v>
       </c>
       <c r="D8" s="109"/>
     </row>
-    <row r="9" spans="3:4" x14ac:dyDescent="0.45">
+    <row r="9" spans="3:4">
       <c r="C9" s="109" t="s">
         <v>20</v>
       </c>
       <c r="D9" s="109"/>
     </row>
-    <row r="10" spans="3:4" x14ac:dyDescent="0.45">
+    <row r="10" spans="3:4">
       <c r="C10" s="161" t="s">
         <v>21</v>
       </c>
       <c r="D10" s="161"/>
     </row>
-    <row r="11" spans="3:4" x14ac:dyDescent="0.45">
+    <row r="11" spans="3:4">
       <c r="C11" s="161" t="s">
         <v>22</v>
       </c>
       <c r="D11" s="161"/>
     </row>
-    <row r="12" spans="3:4" x14ac:dyDescent="0.45">
+    <row r="12" spans="3:4">
       <c r="C12" s="161" t="s">
         <v>23</v>
       </c>
       <c r="D12" s="161"/>
     </row>
-    <row r="13" spans="3:4" x14ac:dyDescent="0.45">
+    <row r="13" spans="3:4">
       <c r="C13" s="161" t="s">
         <v>24</v>
       </c>
@@ -5710,42 +8241,42 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B1:J23"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="28.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="89.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="89.77734375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19" customWidth="1"/>
-    <col min="5" max="5" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.54296875" customWidth="1"/>
-    <col min="7" max="7" width="35.453125" customWidth="1"/>
+    <col min="5" max="5" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5546875" customWidth="1"/>
+    <col min="7" max="7" width="35.44140625" customWidth="1"/>
     <col min="8" max="8" width="38" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="58.453125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="28.81640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="58.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="28.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="211" t="s">
+    <row r="1" spans="2:10" ht="15" customHeight="1" thickBot="1">
+      <c r="B1" s="253" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="212"/>
-      <c r="D1" s="211" t="s">
+      <c r="C1" s="230"/>
+      <c r="D1" s="253" t="s">
         <v>26</v>
       </c>
-      <c r="E1" s="212"/>
-      <c r="F1" s="211" t="s">
+      <c r="E1" s="230"/>
+      <c r="F1" s="253" t="s">
         <v>27</v>
       </c>
-      <c r="G1" s="212"/>
-      <c r="H1" s="209" t="s">
+      <c r="G1" s="230"/>
+      <c r="H1" s="240" t="s">
         <v>28</v>
       </c>
-      <c r="I1" s="210"/>
-      <c r="J1" s="208"/>
-    </row>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="I1" s="232"/>
+      <c r="J1" s="233"/>
+    </row>
+    <row r="2" spans="2:10">
       <c r="B2" s="11" t="s">
         <v>29</v>
       </c>
@@ -5774,7 +8305,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="2:10" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:10" ht="17.100000000000001" customHeight="1">
       <c r="B3" s="12" t="s">
         <v>38</v>
       </c>
@@ -5803,7 +8334,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="2:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:10" ht="15" customHeight="1" thickBot="1">
       <c r="B4" s="12" t="s">
         <v>47</v>
       </c>
@@ -5830,7 +8361,7 @@
       </c>
       <c r="J4" s="5"/>
     </row>
-    <row r="5" spans="2:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:10" ht="15" customHeight="1" thickBot="1">
       <c r="B5" s="12" t="s">
         <v>0</v>
       </c>
@@ -5853,7 +8384,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="6" spans="2:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:10" ht="15" customHeight="1" thickBot="1">
       <c r="B6" s="12" t="s">
         <v>60</v>
       </c>
@@ -5876,7 +8407,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="2:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:10" ht="15" customHeight="1" thickBot="1">
       <c r="B7" s="12" t="s">
         <v>65</v>
       </c>
@@ -5899,7 +8430,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="8" spans="2:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:10" ht="15" customHeight="1" thickBot="1">
       <c r="B8" s="12" t="s">
         <v>71</v>
       </c>
@@ -5913,7 +8444,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:10">
       <c r="B9" s="37" t="s">
         <v>74</v>
       </c>
@@ -5927,7 +8458,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="10" spans="2:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:10" ht="15" customHeight="1" thickBot="1">
       <c r="B10" s="12" t="s">
         <v>77</v>
       </c>
@@ -5941,7 +8472,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="11" spans="2:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:10" ht="15" customHeight="1" thickBot="1">
       <c r="B11" s="12" t="s">
         <v>80</v>
       </c>
@@ -5949,7 +8480,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="12" spans="2:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:10" ht="15" customHeight="1" thickBot="1">
       <c r="B12" s="12" t="s">
         <v>82</v>
       </c>
@@ -5963,7 +8494,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="13" spans="2:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:10" ht="15" customHeight="1" thickBot="1">
       <c r="B13" s="12" t="s">
         <v>86</v>
       </c>
@@ -5977,7 +8508,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:10">
       <c r="B14" s="12" t="s">
         <v>89</v>
       </c>
@@ -5985,7 +8516,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:10">
       <c r="B15" s="12" t="s">
         <v>91</v>
       </c>
@@ -5993,7 +8524,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:10">
       <c r="B16" s="12" t="s">
         <v>93</v>
       </c>
@@ -6001,7 +8532,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:3">
       <c r="B17" s="12" t="s">
         <v>95</v>
       </c>
@@ -6009,7 +8540,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:3">
       <c r="B18" s="12" t="s">
         <v>97</v>
       </c>
@@ -6017,7 +8548,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:3">
       <c r="B19" s="12" t="s">
         <v>99</v>
       </c>
@@ -6025,7 +8556,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:3">
       <c r="B20" s="12" t="s">
         <v>101</v>
       </c>
@@ -6033,19 +8564,19 @@
         <v>102</v>
       </c>
     </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:3">
       <c r="B21" s="37" t="s">
         <v>103</v>
       </c>
       <c r="C21" s="38"/>
     </row>
-    <row r="22" spans="2:3" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:3" ht="15" customHeight="1" thickBot="1">
       <c r="B22" s="3" t="s">
         <v>104</v>
       </c>
       <c r="C22" s="14"/>
     </row>
-    <row r="23" spans="2:3" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:3" ht="15" customHeight="1" thickBot="1">
       <c r="B23" s="3" t="s">
         <v>105</v>
       </c>
@@ -6062,22 +8593,22 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B2:C6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="43.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="91.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="91.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:3">
       <c r="B2" s="156" t="s">
         <v>63</v>
       </c>
       <c r="C2" s="156"/>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:3">
       <c r="B3" s="155" t="s">
         <v>106</v>
       </c>
@@ -6085,7 +8616,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:3">
       <c r="B4" s="33" t="s">
         <v>107</v>
       </c>
@@ -6093,7 +8624,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:3">
       <c r="B5" s="33" t="s">
         <v>109</v>
       </c>
@@ -6101,7 +8632,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:3">
       <c r="B6" s="33" t="s">
         <v>111</v>
       </c>
@@ -6114,30 +8645,29 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="B1:O113"/>
-  <sheetFormatPr defaultColWidth="13" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="13" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="9.1796875" style="17" customWidth="1"/>
-    <col min="2" max="2" width="45.1796875" style="17" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.1796875" style="17" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.26953125" style="17" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.54296875" style="17" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.54296875" style="17" customWidth="1"/>
-    <col min="7" max="7" width="19.54296875" style="267" customWidth="1"/>
-    <col min="8" max="8" width="39.54296875" style="17" customWidth="1"/>
+    <col min="1" max="1" width="9.21875" style="17" customWidth="1"/>
+    <col min="2" max="2" width="45.21875" style="17" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.21875" style="17" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.21875" style="17" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5546875" style="17" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="19.5546875" style="17" customWidth="1"/>
+    <col min="8" max="8" width="39.5546875" style="17" customWidth="1"/>
     <col min="9" max="9" width="9" style="17" customWidth="1"/>
-    <col min="10" max="10" width="33.7265625" style="17" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.54296875" style="17" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="33.77734375" style="17" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.5546875" style="17" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="44" style="17" customWidth="1"/>
     <col min="13" max="13" width="72" style="17" customWidth="1"/>
     <col min="14" max="14" width="48" style="17" customWidth="1"/>
     <col min="15" max="15" width="13" style="17" customWidth="1"/>
-    <col min="16" max="16" width="25.453125" style="17" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="19.81640625" style="17" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.7265625" style="17" customWidth="1"/>
-    <col min="19" max="248" width="9.1796875" style="17" customWidth="1"/>
+    <col min="16" max="16" width="25.44140625" style="17" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="19.77734375" style="17" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.77734375" style="17" customWidth="1"/>
+    <col min="19" max="248" width="9.21875" style="17" customWidth="1"/>
     <col min="249" max="249" width="7" style="17" bestFit="1" customWidth="1"/>
     <col min="250" max="250" width="14" style="17" customWidth="1"/>
     <col min="251" max="251" width="11" style="17" customWidth="1"/>
@@ -6145,79 +8675,77 @@
     <col min="253" max="16384" width="13" style="17"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" s="34" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G1" s="264"/>
+    <row r="1" spans="2:14" s="34" customFormat="1" ht="13.5" customHeight="1">
       <c r="H1" s="88"/>
       <c r="I1" s="88"/>
     </row>
-    <row r="2" spans="2:14" s="34" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B2" s="268" t="s">
+    <row r="2" spans="2:14" s="34" customFormat="1" ht="30" customHeight="1" thickBot="1">
+      <c r="B2" s="209" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="264"/>
       <c r="H2" s="88"/>
       <c r="I2" s="88"/>
-      <c r="L2" s="226" t="s">
+      <c r="L2" s="241" t="s">
         <v>114</v>
       </c>
-      <c r="M2" s="225"/>
-      <c r="N2" s="225"/>
-    </row>
-    <row r="3" spans="2:14" s="35" customFormat="1" ht="32.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="269" t="s">
+      <c r="M2" s="242"/>
+      <c r="N2" s="242"/>
+    </row>
+    <row r="3" spans="2:14" s="35" customFormat="1" ht="32.1" customHeight="1">
+      <c r="B3" s="247" t="s">
         <v>115</v>
       </c>
-      <c r="C3" s="269" t="s">
+      <c r="C3" s="247" t="s">
         <v>116</v>
       </c>
-      <c r="D3" s="270"/>
-      <c r="E3" s="270"/>
-      <c r="F3" s="269" t="s">
+      <c r="D3" s="248"/>
+      <c r="E3" s="248"/>
+      <c r="F3" s="247" t="s">
         <v>117</v>
       </c>
-      <c r="G3" s="265"/>
-      <c r="H3" s="240" t="s">
+      <c r="G3" s="208"/>
+      <c r="H3" s="226" t="s">
         <v>118</v>
       </c>
-      <c r="I3" s="241"/>
-      <c r="J3" s="227" t="s">
+      <c r="I3" s="227"/>
+      <c r="J3" s="243" t="s">
         <v>119</v>
       </c>
-      <c r="K3" s="227" t="s">
+      <c r="K3" s="243" t="s">
         <v>120</v>
       </c>
-      <c r="L3" s="217" t="s">
+      <c r="L3" s="218" t="s">
         <v>121</v>
       </c>
-      <c r="M3" s="217" t="s">
+      <c r="M3" s="218" t="s">
         <v>122</v>
       </c>
-      <c r="N3" s="217" t="s">
+      <c r="N3" s="218" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="4" spans="2:14" s="35" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="270"/>
-      <c r="C4" s="271" t="s">
+    <row r="4" spans="2:14" s="35" customFormat="1" ht="15" customHeight="1" thickBot="1">
+      <c r="B4" s="248"/>
+      <c r="C4" s="210" t="s">
         <v>124</v>
       </c>
-      <c r="D4" s="271" t="s">
+      <c r="D4" s="210" t="s">
         <v>125</v>
       </c>
-      <c r="E4" s="271" t="s">
+      <c r="E4" s="210" t="s">
         <v>126</v>
       </c>
-      <c r="F4" s="270"/>
-      <c r="G4" s="257"/>
-      <c r="H4" s="242"/>
-      <c r="I4" s="218"/>
-      <c r="J4" s="228"/>
-      <c r="K4" s="228"/>
-      <c r="L4" s="218"/>
-      <c r="M4" s="218"/>
-      <c r="N4" s="218"/>
-    </row>
-    <row r="5" spans="2:14" s="34" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F4" s="248"/>
+      <c r="G4"/>
+      <c r="H4" s="228"/>
+      <c r="I4" s="219"/>
+      <c r="J4" s="244"/>
+      <c r="K4" s="244"/>
+      <c r="L4" s="219"/>
+      <c r="M4" s="219"/>
+      <c r="N4" s="219"/>
+    </row>
+    <row r="5" spans="2:14" s="34" customFormat="1" ht="54" customHeight="1">
       <c r="B5" s="19" t="s">
         <v>127</v>
       </c>
@@ -6233,11 +8761,11 @@
       <c r="F5" s="19" t="s">
         <v>129</v>
       </c>
-      <c r="G5" s="258"/>
-      <c r="H5" s="229" t="s">
+      <c r="G5" s="18"/>
+      <c r="H5" s="245" t="s">
         <v>130</v>
       </c>
-      <c r="I5" s="223"/>
+      <c r="I5" s="246"/>
       <c r="J5" s="137" t="s">
         <v>131</v>
       </c>
@@ -6254,7 +8782,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="6" spans="2:14" s="34" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:14" s="34" customFormat="1" ht="54" customHeight="1">
       <c r="B6" s="19" t="s">
         <v>135</v>
       </c>
@@ -6270,11 +8798,11 @@
       <c r="F6" s="19" t="s">
         <v>129</v>
       </c>
-      <c r="G6" s="258"/>
-      <c r="H6" s="215" t="s">
+      <c r="G6" s="18"/>
+      <c r="H6" s="220" t="s">
         <v>136</v>
       </c>
-      <c r="I6" s="216"/>
+      <c r="I6" s="221"/>
       <c r="J6" s="138" t="s">
         <v>137</v>
       </c>
@@ -6291,7 +8819,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="7" spans="2:14" s="34" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:14" s="34" customFormat="1" ht="54" customHeight="1">
       <c r="B7" s="19" t="s">
         <v>141</v>
       </c>
@@ -6307,11 +8835,11 @@
       <c r="F7" s="19" t="s">
         <v>142</v>
       </c>
-      <c r="G7" s="258"/>
-      <c r="H7" s="215" t="s">
+      <c r="G7" s="18"/>
+      <c r="H7" s="220" t="s">
         <v>143</v>
       </c>
-      <c r="I7" s="216"/>
+      <c r="I7" s="221"/>
       <c r="J7" s="138" t="s">
         <v>144</v>
       </c>
@@ -6328,7 +8856,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="8" spans="2:14" s="34" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:14" s="34" customFormat="1" ht="54" customHeight="1">
       <c r="B8" s="19" t="s">
         <v>148</v>
       </c>
@@ -6344,11 +8872,11 @@
       <c r="F8" s="19" t="s">
         <v>142</v>
       </c>
-      <c r="G8" s="258"/>
-      <c r="H8" s="215" t="s">
+      <c r="G8" s="18"/>
+      <c r="H8" s="220" t="s">
         <v>149</v>
       </c>
-      <c r="I8" s="216"/>
+      <c r="I8" s="221"/>
       <c r="J8" s="138" t="s">
         <v>144</v>
       </c>
@@ -6365,7 +8893,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="9" spans="2:14" s="34" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:14" s="34" customFormat="1" ht="54" customHeight="1">
       <c r="B9" s="19" t="s">
         <v>153</v>
       </c>
@@ -6381,11 +8909,11 @@
       <c r="F9" s="19" t="s">
         <v>142</v>
       </c>
-      <c r="G9" s="258"/>
-      <c r="H9" s="215" t="s">
+      <c r="G9" s="18"/>
+      <c r="H9" s="220" t="s">
         <v>154</v>
       </c>
-      <c r="I9" s="216"/>
+      <c r="I9" s="221"/>
       <c r="J9" s="138" t="s">
         <v>137</v>
       </c>
@@ -6402,7 +8930,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="10" spans="2:14" s="34" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:14" s="34" customFormat="1" ht="54" customHeight="1">
       <c r="B10" s="19" t="s">
         <v>158</v>
       </c>
@@ -6418,11 +8946,11 @@
       <c r="F10" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="G10" s="258"/>
-      <c r="H10" s="215" t="s">
+      <c r="G10" s="18"/>
+      <c r="H10" s="220" t="s">
         <v>159</v>
       </c>
-      <c r="I10" s="216"/>
+      <c r="I10" s="221"/>
       <c r="J10" s="138" t="s">
         <v>137</v>
       </c>
@@ -6439,7 +8967,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="11" spans="2:14" s="34" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:14" s="34" customFormat="1" ht="54" customHeight="1">
       <c r="B11" s="19" t="s">
         <v>164</v>
       </c>
@@ -6455,11 +8983,11 @@
       <c r="F11" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="G11" s="258"/>
-      <c r="H11" s="215" t="s">
+      <c r="G11" s="18"/>
+      <c r="H11" s="220" t="s">
         <v>165</v>
       </c>
-      <c r="I11" s="216"/>
+      <c r="I11" s="221"/>
       <c r="J11" s="138" t="s">
         <v>137</v>
       </c>
@@ -6476,7 +9004,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="12" spans="2:14" s="34" customFormat="1" ht="54" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:14" s="34" customFormat="1" ht="54" customHeight="1" thickBot="1">
       <c r="B12" s="19" t="s">
         <v>169</v>
       </c>
@@ -6486,11 +9014,11 @@
       <c r="F12" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="G12" s="258"/>
-      <c r="H12" s="213" t="s">
+      <c r="G12" s="18"/>
+      <c r="H12" s="216" t="s">
         <v>171</v>
       </c>
-      <c r="I12" s="214"/>
+      <c r="I12" s="217"/>
       <c r="J12" s="139" t="s">
         <v>137</v>
       </c>
@@ -6507,7 +9035,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="13" spans="2:14" s="34" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:14" s="34" customFormat="1" ht="14.55" customHeight="1">
       <c r="B13" s="19" t="s">
         <v>175</v>
       </c>
@@ -6517,9 +9045,9 @@
       <c r="F13" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="G13" s="258"/>
-    </row>
-    <row r="14" spans="2:14" s="34" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G13" s="18"/>
+    </row>
+    <row r="14" spans="2:14" s="34" customFormat="1" ht="14.55" customHeight="1">
       <c r="B14" s="19" t="s">
         <v>176</v>
       </c>
@@ -6529,13 +9057,13 @@
       <c r="F14" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="G14" s="258"/>
-      <c r="H14" s="224"/>
-      <c r="I14" s="225"/>
+      <c r="G14" s="18"/>
+      <c r="H14" s="251"/>
+      <c r="I14" s="242"/>
       <c r="J14" s="65"/>
       <c r="K14" s="65"/>
     </row>
-    <row r="15" spans="2:14" s="34" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:14" s="34" customFormat="1" ht="14.55" customHeight="1">
       <c r="B15" s="19" t="s">
         <v>177</v>
       </c>
@@ -6545,12 +9073,12 @@
       <c r="F15" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="G15" s="258"/>
+      <c r="G15" s="18"/>
       <c r="H15" s="88"/>
       <c r="I15" s="88"/>
       <c r="J15" s="140"/>
     </row>
-    <row r="16" spans="2:14" s="34" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:14" s="34" customFormat="1" ht="14.55" customHeight="1">
       <c r="B16" s="19" t="s">
         <v>178</v>
       </c>
@@ -6560,11 +9088,11 @@
       <c r="F16" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="G16" s="258"/>
+      <c r="G16" s="18"/>
       <c r="H16" s="88"/>
       <c r="I16" s="88"/>
     </row>
-    <row r="17" spans="2:9" s="34" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:9" s="34" customFormat="1" ht="14.55" customHeight="1">
       <c r="B17" s="19" t="s">
         <v>179</v>
       </c>
@@ -6574,11 +9102,11 @@
       <c r="F17" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="G17" s="258"/>
+      <c r="G17" s="18"/>
       <c r="H17" s="88"/>
       <c r="I17" s="88"/>
     </row>
-    <row r="18" spans="2:9" s="34" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:9" s="34" customFormat="1" ht="14.55" customHeight="1">
       <c r="B18" s="19" t="s">
         <v>180</v>
       </c>
@@ -6588,11 +9116,11 @@
       <c r="F18" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="G18" s="258"/>
+      <c r="G18" s="18"/>
       <c r="H18" s="88"/>
       <c r="I18" s="88"/>
     </row>
-    <row r="19" spans="2:9" s="34" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:9" s="34" customFormat="1" ht="14.55" customHeight="1">
       <c r="B19" s="19" t="s">
         <v>181</v>
       </c>
@@ -6602,11 +9130,11 @@
       <c r="F19" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="G19" s="258"/>
+      <c r="G19" s="18"/>
       <c r="H19" s="88"/>
       <c r="I19" s="88"/>
     </row>
-    <row r="20" spans="2:9" s="34" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:9" s="34" customFormat="1" ht="14.55" customHeight="1">
       <c r="B20" s="19" t="s">
         <v>182</v>
       </c>
@@ -6616,11 +9144,11 @@
       <c r="F20" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="G20" s="258"/>
+      <c r="G20" s="18"/>
       <c r="H20" s="88"/>
       <c r="I20" s="88"/>
     </row>
-    <row r="21" spans="2:9" s="34" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:9" s="34" customFormat="1" ht="14.55" customHeight="1">
       <c r="B21" s="19" t="s">
         <v>183</v>
       </c>
@@ -6630,11 +9158,11 @@
       <c r="F21" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="G21" s="258"/>
+      <c r="G21" s="18"/>
       <c r="H21" s="88"/>
       <c r="I21" s="88"/>
     </row>
-    <row r="22" spans="2:9" s="34" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:9" s="34" customFormat="1" ht="14.55" customHeight="1">
       <c r="B22" s="19" t="s">
         <v>184</v>
       </c>
@@ -6644,11 +9172,11 @@
       <c r="F22" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="G22" s="258"/>
+      <c r="G22" s="18"/>
       <c r="H22" s="88"/>
       <c r="I22" s="88"/>
     </row>
-    <row r="23" spans="2:9" s="34" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:9" s="34" customFormat="1" ht="14.55" customHeight="1">
       <c r="B23" s="19" t="s">
         <v>185</v>
       </c>
@@ -6658,11 +9186,11 @@
       <c r="F23" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="G23" s="258"/>
+      <c r="G23" s="18"/>
       <c r="H23" s="88"/>
       <c r="I23" s="88"/>
     </row>
-    <row r="24" spans="2:9" s="34" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:9" s="34" customFormat="1" ht="14.55" customHeight="1">
       <c r="B24" s="19" t="s">
         <v>186</v>
       </c>
@@ -6672,11 +9200,11 @@
       <c r="F24" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="G24" s="258"/>
+      <c r="G24" s="18"/>
       <c r="H24" s="88"/>
       <c r="I24" s="88"/>
     </row>
-    <row r="25" spans="2:9" s="34" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:9" s="34" customFormat="1" ht="14.55" customHeight="1">
       <c r="B25" s="19" t="s">
         <v>187</v>
       </c>
@@ -6686,11 +9214,11 @@
       <c r="F25" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="G25" s="258"/>
+      <c r="G25" s="18"/>
       <c r="H25" s="88"/>
       <c r="I25" s="88"/>
     </row>
-    <row r="26" spans="2:9" s="34" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:9" s="34" customFormat="1" ht="14.55" customHeight="1">
       <c r="B26" s="19" t="s">
         <v>188</v>
       </c>
@@ -6700,11 +9228,11 @@
       <c r="F26" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="G26" s="258"/>
+      <c r="G26" s="18"/>
       <c r="H26" s="88"/>
       <c r="I26" s="88"/>
     </row>
-    <row r="27" spans="2:9" s="34" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:9" s="34" customFormat="1" ht="14.55" customHeight="1">
       <c r="B27" s="19" t="s">
         <v>189</v>
       </c>
@@ -6714,11 +9242,11 @@
       <c r="F27" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="G27" s="258"/>
+      <c r="G27" s="18"/>
       <c r="H27" s="88"/>
       <c r="I27" s="88"/>
     </row>
-    <row r="28" spans="2:9" s="34" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:9" s="34" customFormat="1" ht="14.55" customHeight="1">
       <c r="B28" s="19" t="s">
         <v>190</v>
       </c>
@@ -6728,11 +9256,11 @@
       <c r="F28" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="G28" s="258"/>
+      <c r="G28" s="18"/>
       <c r="H28" s="88"/>
       <c r="I28" s="88"/>
     </row>
-    <row r="29" spans="2:9" s="34" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:9" s="34" customFormat="1" ht="14.55" customHeight="1">
       <c r="B29" s="19" t="s">
         <v>191</v>
       </c>
@@ -6742,11 +9270,11 @@
       <c r="F29" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="G29" s="258"/>
+      <c r="G29" s="18"/>
       <c r="H29" s="88"/>
       <c r="I29" s="88"/>
     </row>
-    <row r="30" spans="2:9" s="34" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:9" s="34" customFormat="1" ht="14.55" customHeight="1">
       <c r="B30" s="19" t="s">
         <v>192</v>
       </c>
@@ -6756,11 +9284,11 @@
       <c r="F30" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="G30" s="258"/>
+      <c r="G30" s="18"/>
       <c r="H30" s="88"/>
       <c r="I30" s="88"/>
     </row>
-    <row r="31" spans="2:9" s="34" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:9" s="34" customFormat="1" ht="14.55" customHeight="1">
       <c r="B31" s="19" t="s">
         <v>193</v>
       </c>
@@ -6770,11 +9298,11 @@
       <c r="F31" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="G31" s="258"/>
+      <c r="G31" s="18"/>
       <c r="H31" s="88"/>
       <c r="I31" s="88"/>
     </row>
-    <row r="32" spans="2:9" s="34" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:9" s="34" customFormat="1" ht="14.55" customHeight="1">
       <c r="B32" s="19" t="s">
         <v>194</v>
       </c>
@@ -6784,11 +9312,11 @@
       <c r="F32" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="G32" s="258"/>
+      <c r="G32" s="18"/>
       <c r="H32" s="88"/>
       <c r="I32" s="88"/>
     </row>
-    <row r="33" spans="2:14" s="34" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:14" s="34" customFormat="1" ht="14.55" customHeight="1">
       <c r="B33" s="19" t="s">
         <v>195</v>
       </c>
@@ -6798,11 +9326,11 @@
       <c r="F33" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="G33" s="258"/>
+      <c r="G33" s="18"/>
       <c r="H33" s="88"/>
       <c r="I33" s="88"/>
     </row>
-    <row r="34" spans="2:14" s="34" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:14" s="34" customFormat="1" ht="14.55" customHeight="1">
       <c r="B34" s="19" t="s">
         <v>196</v>
       </c>
@@ -6812,11 +9340,11 @@
       <c r="F34" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="G34" s="258"/>
+      <c r="G34" s="18"/>
       <c r="H34" s="88"/>
       <c r="I34" s="88"/>
     </row>
-    <row r="35" spans="2:14" s="34" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:14" s="34" customFormat="1" ht="14.55" customHeight="1">
       <c r="B35" s="19" t="s">
         <v>197</v>
       </c>
@@ -6826,11 +9354,11 @@
       <c r="F35" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="G35" s="258"/>
+      <c r="G35" s="18"/>
       <c r="H35" s="88"/>
       <c r="I35" s="88"/>
     </row>
-    <row r="36" spans="2:14" s="34" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:14" s="34" customFormat="1" ht="14.55" customHeight="1">
       <c r="B36" s="19" t="s">
         <v>198</v>
       </c>
@@ -6840,11 +9368,11 @@
       <c r="F36" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="G36" s="258"/>
+      <c r="G36" s="18"/>
       <c r="H36" s="88"/>
       <c r="I36" s="88"/>
     </row>
-    <row r="37" spans="2:14" s="34" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:14" s="34" customFormat="1" ht="14.55" customHeight="1">
       <c r="B37" s="19" t="s">
         <v>199</v>
       </c>
@@ -6860,11 +9388,11 @@
       <c r="F37" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="G37" s="258"/>
+      <c r="G37" s="18"/>
       <c r="H37" s="88"/>
       <c r="I37" s="88"/>
     </row>
-    <row r="38" spans="2:14" s="34" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:14" s="34" customFormat="1" ht="14.55" customHeight="1">
       <c r="B38" s="19" t="s">
         <v>200</v>
       </c>
@@ -6880,11 +9408,11 @@
       <c r="F38" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="G38" s="258"/>
+      <c r="G38" s="18"/>
       <c r="H38" s="88"/>
       <c r="I38" s="88"/>
     </row>
-    <row r="39" spans="2:14" s="34" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:14" s="34" customFormat="1" ht="15" customHeight="1">
       <c r="B39" s="19" t="s">
         <v>201</v>
       </c>
@@ -6898,31 +9426,31 @@
         <v>128</v>
       </c>
       <c r="F39" s="19"/>
-      <c r="G39" s="258"/>
+      <c r="G39" s="18"/>
       <c r="H39" s="88"/>
       <c r="I39" s="88"/>
     </row>
-    <row r="40" spans="2:14" s="34" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:14" s="34" customFormat="1" ht="14.55" customHeight="1">
       <c r="B40" s="18"/>
       <c r="C40" s="18"/>
       <c r="D40" s="18"/>
       <c r="E40" s="18"/>
       <c r="F40" s="18"/>
-      <c r="G40" s="258"/>
+      <c r="G40" s="18"/>
       <c r="H40" s="88"/>
       <c r="I40" s="88"/>
     </row>
-    <row r="41" spans="2:14" s="34" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:14" s="34" customFormat="1" ht="14.55" customHeight="1">
       <c r="B41" s="18"/>
       <c r="C41" s="18"/>
       <c r="D41" s="18"/>
       <c r="E41" s="18"/>
       <c r="F41" s="18"/>
-      <c r="G41" s="258"/>
+      <c r="G41" s="18"/>
       <c r="H41" s="88"/>
       <c r="I41" s="88"/>
     </row>
-    <row r="42" spans="2:14" s="64" customFormat="1" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="42" spans="2:14" s="64" customFormat="1" ht="19.05" customHeight="1" thickBot="1">
       <c r="B42" s="119" t="s">
         <v>202</v>
       </c>
@@ -6930,23 +9458,23 @@
       <c r="D42" s="25"/>
       <c r="E42" s="25"/>
       <c r="F42" s="25"/>
-      <c r="G42" s="266"/>
+      <c r="G42" s="25"/>
       <c r="H42" s="89"/>
       <c r="I42" s="89"/>
     </row>
-    <row r="43" spans="2:14" s="34" customFormat="1" ht="32.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B43" s="232" t="s">
+    <row r="43" spans="2:14" s="34" customFormat="1" ht="32.1" customHeight="1" thickBot="1">
+      <c r="B43" s="231" t="s">
         <v>203</v>
       </c>
-      <c r="C43" s="210"/>
-      <c r="D43" s="210"/>
-      <c r="E43" s="208"/>
+      <c r="C43" s="232"/>
+      <c r="D43" s="232"/>
+      <c r="E43" s="233"/>
       <c r="F43" s="18"/>
-      <c r="G43" s="258"/>
-      <c r="H43" s="209" t="s">
+      <c r="G43" s="18"/>
+      <c r="H43" s="240" t="s">
         <v>118</v>
       </c>
-      <c r="I43" s="208"/>
+      <c r="I43" s="233"/>
       <c r="J43" s="141" t="s">
         <v>119</v>
       </c>
@@ -6960,22 +9488,21 @@
         <v>123</v>
       </c>
     </row>
-    <row r="44" spans="2:14" s="18" customFormat="1" ht="54" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="2:14" s="18" customFormat="1" ht="54" customHeight="1" thickBot="1">
       <c r="B44" s="117" t="s">
         <v>204</v>
       </c>
       <c r="C44" s="118" t="s">
         <v>116</v>
       </c>
-      <c r="D44" s="232" t="s">
+      <c r="D44" s="231" t="s">
         <v>117</v>
       </c>
-      <c r="E44" s="208"/>
-      <c r="G44" s="258"/>
-      <c r="H44" s="237" t="s">
+      <c r="E44" s="233"/>
+      <c r="H44" s="222" t="s">
         <v>205</v>
       </c>
-      <c r="I44" s="238"/>
+      <c r="I44" s="223"/>
       <c r="J44" s="142" t="s">
         <v>137</v>
       </c>
@@ -6989,8 +9516,8 @@
         <v>208</v>
       </c>
     </row>
-    <row r="45" spans="2:14" s="18" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B45" s="219" t="s">
+    <row r="45" spans="2:14" s="18" customFormat="1" ht="54" customHeight="1">
+      <c r="B45" s="224" t="s">
         <v>209</v>
       </c>
       <c r="C45" s="69" t="s">
@@ -7002,11 +9529,10 @@
       <c r="E45" s="71" t="s">
         <v>211</v>
       </c>
-      <c r="G45" s="258"/>
-      <c r="H45" s="233" t="s">
+      <c r="H45" s="212" t="s">
         <v>212</v>
       </c>
-      <c r="I45" s="234"/>
+      <c r="I45" s="213"/>
       <c r="J45" s="136" t="s">
         <v>213</v>
       </c>
@@ -7020,8 +9546,8 @@
         <v>216</v>
       </c>
     </row>
-    <row r="46" spans="2:14" s="18" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B46" s="220"/>
+    <row r="46" spans="2:14" s="18" customFormat="1" ht="54" customHeight="1">
+      <c r="B46" s="238"/>
       <c r="C46" s="67" t="s">
         <v>217</v>
       </c>
@@ -7031,11 +9557,10 @@
       <c r="E46" s="72" t="s">
         <v>211</v>
       </c>
-      <c r="G46" s="258"/>
-      <c r="H46" s="233" t="s">
+      <c r="H46" s="212" t="s">
         <v>218</v>
       </c>
-      <c r="I46" s="234"/>
+      <c r="I46" s="213"/>
       <c r="J46" s="136" t="s">
         <v>219</v>
       </c>
@@ -7049,8 +9574,8 @@
         <v>222</v>
       </c>
     </row>
-    <row r="47" spans="2:14" s="18" customFormat="1" ht="54" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B47" s="221"/>
+    <row r="47" spans="2:14" s="18" customFormat="1" ht="54" customHeight="1" thickBot="1">
+      <c r="B47" s="239"/>
       <c r="C47" s="67" t="s">
         <v>223</v>
       </c>
@@ -7060,11 +9585,10 @@
       <c r="E47" s="72" t="s">
         <v>211</v>
       </c>
-      <c r="G47" s="258"/>
-      <c r="H47" s="230" t="s">
+      <c r="H47" s="214" t="s">
         <v>224</v>
       </c>
-      <c r="I47" s="231"/>
+      <c r="I47" s="215"/>
       <c r="J47" s="85" t="s">
         <v>225</v>
       </c>
@@ -7078,7 +9602,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="48" spans="2:14" s="18" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:14" s="18" customFormat="1" ht="14.55" customHeight="1">
       <c r="B48" s="20" t="s">
         <v>229</v>
       </c>
@@ -7091,12 +9615,11 @@
       <c r="E48" s="72" t="s">
         <v>211</v>
       </c>
-      <c r="G48" s="258"/>
       <c r="H48" s="65"/>
       <c r="I48" s="65"/>
       <c r="J48" s="65"/>
     </row>
-    <row r="49" spans="2:15" s="25" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="2:15" s="25" customFormat="1" ht="15" customHeight="1" thickBot="1">
       <c r="B49" s="20" t="s">
         <v>230</v>
       </c>
@@ -7109,12 +9632,11 @@
       <c r="E49" s="82" t="s">
         <v>211</v>
       </c>
-      <c r="G49" s="266"/>
       <c r="H49" s="90"/>
       <c r="I49" s="90"/>
       <c r="O49" s="26"/>
     </row>
-    <row r="50" spans="2:15" s="18" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:15" s="18" customFormat="1" ht="14.55" customHeight="1">
       <c r="B50" s="20" t="s">
         <v>231</v>
       </c>
@@ -7124,11 +9646,10 @@
       <c r="D50" s="21" t="s">
         <v>170</v>
       </c>
-      <c r="G50" s="258"/>
       <c r="H50" s="66"/>
       <c r="I50" s="66"/>
     </row>
-    <row r="51" spans="2:15" s="18" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:15" s="18" customFormat="1" ht="14.55" customHeight="1">
       <c r="B51" s="20" t="s">
         <v>232</v>
       </c>
@@ -7138,11 +9659,10 @@
       <c r="D51" s="21" t="s">
         <v>170</v>
       </c>
-      <c r="G51" s="258"/>
       <c r="H51" s="66"/>
       <c r="I51" s="66"/>
     </row>
-    <row r="52" spans="2:15" s="18" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="2:15" s="18" customFormat="1" ht="15" customHeight="1" thickBot="1">
       <c r="B52" s="22" t="s">
         <v>233</v>
       </c>
@@ -7152,29 +9672,25 @@
       <c r="D52" s="24" t="s">
         <v>170</v>
       </c>
-      <c r="G52" s="258"/>
       <c r="H52" s="66"/>
       <c r="I52" s="66"/>
     </row>
-    <row r="53" spans="2:15" s="18" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="G53" s="258"/>
+    <row r="53" spans="2:15" s="18" customFormat="1" ht="14.55" customHeight="1">
       <c r="H53" s="66"/>
       <c r="I53" s="66"/>
     </row>
-    <row r="54" spans="2:15" s="18" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="G54" s="258"/>
+    <row r="54" spans="2:15" s="18" customFormat="1" ht="14.55" customHeight="1">
       <c r="H54" s="66"/>
       <c r="I54" s="66"/>
     </row>
-    <row r="55" spans="2:15" s="18" customFormat="1" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="55" spans="2:15" s="18" customFormat="1" ht="19.05" customHeight="1" thickBot="1">
       <c r="B55" s="119" t="s">
         <v>6</v>
       </c>
-      <c r="G55" s="258"/>
       <c r="H55" s="66"/>
       <c r="I55" s="66"/>
     </row>
-    <row r="56" spans="2:15" s="18" customFormat="1" ht="32.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="2:15" s="18" customFormat="1" ht="32.1" customHeight="1" thickBot="1">
       <c r="B56" s="120" t="s">
         <v>115</v>
       </c>
@@ -7182,7 +9698,6 @@
       <c r="D56" s="122" t="s">
         <v>234</v>
       </c>
-      <c r="G56" s="258"/>
       <c r="H56" s="115" t="s">
         <v>118</v>
       </c>
@@ -7200,7 +9715,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="57" spans="2:15" s="18" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:15" s="18" customFormat="1" ht="54" customHeight="1">
       <c r="B57" s="43" t="s">
         <v>235</v>
       </c>
@@ -7211,8 +9726,7 @@
         <v>170</v>
       </c>
       <c r="E57" s="25"/>
-      <c r="G57" s="258"/>
-      <c r="H57" s="259" t="s">
+      <c r="H57" s="249" t="s">
         <v>236</v>
       </c>
       <c r="I57" s="91" t="s">
@@ -7231,8 +9745,8 @@
         <v>241</v>
       </c>
     </row>
-    <row r="58" spans="2:15" s="18" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B58" s="222" t="s">
+    <row r="58" spans="2:15" s="18" customFormat="1" ht="14.55" customHeight="1">
+      <c r="B58" s="237" t="s">
         <v>242</v>
       </c>
       <c r="C58" s="46" t="s">
@@ -7241,8 +9755,7 @@
       <c r="D58" s="21" t="s">
         <v>243</v>
       </c>
-      <c r="G58" s="258"/>
-      <c r="H58" s="260"/>
+      <c r="H58" s="235"/>
       <c r="I58" s="92" t="s">
         <v>244</v>
       </c>
@@ -7250,16 +9763,15 @@
         <v>238</v>
       </c>
     </row>
-    <row r="59" spans="2:15" s="18" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B59" s="220"/>
+    <row r="59" spans="2:15" s="18" customFormat="1" ht="14.55" customHeight="1">
+      <c r="B59" s="238"/>
       <c r="C59" s="46" t="s">
         <v>244</v>
       </c>
       <c r="D59" s="21" t="s">
         <v>243</v>
       </c>
-      <c r="G59" s="258"/>
-      <c r="H59" s="260"/>
+      <c r="H59" s="235"/>
       <c r="I59" s="92" t="s">
         <v>245</v>
       </c>
@@ -7267,16 +9779,15 @@
         <v>238</v>
       </c>
     </row>
-    <row r="60" spans="2:15" s="18" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B60" s="220"/>
+    <row r="60" spans="2:15" s="18" customFormat="1" ht="14.55" customHeight="1">
+      <c r="B60" s="238"/>
       <c r="C60" s="46" t="s">
         <v>245</v>
       </c>
       <c r="D60" s="21" t="s">
         <v>243</v>
       </c>
-      <c r="G60" s="258"/>
-      <c r="H60" s="261"/>
+      <c r="H60" s="250"/>
       <c r="I60" s="92" t="s">
         <v>246</v>
       </c>
@@ -7284,16 +9795,15 @@
         <v>238</v>
       </c>
     </row>
-    <row r="61" spans="2:15" s="18" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B61" s="221"/>
+    <row r="61" spans="2:15" s="18" customFormat="1" ht="54" customHeight="1">
+      <c r="B61" s="239"/>
       <c r="C61" s="46" t="s">
         <v>246</v>
       </c>
       <c r="D61" s="21" t="s">
         <v>243</v>
       </c>
-      <c r="G61" s="258"/>
-      <c r="H61" s="262" t="s">
+      <c r="H61" s="207" t="s">
         <v>247</v>
       </c>
       <c r="I61" s="87"/>
@@ -7310,7 +9820,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="62" spans="2:15" s="18" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:15" s="18" customFormat="1" ht="54" customHeight="1">
       <c r="B62" s="47" t="s">
         <v>251</v>
       </c>
@@ -7320,8 +9830,7 @@
       <c r="D62" s="21" t="s">
         <v>170</v>
       </c>
-      <c r="G62" s="258"/>
-      <c r="H62" s="262" t="s">
+      <c r="H62" s="207" t="s">
         <v>252</v>
       </c>
       <c r="I62" s="87"/>
@@ -7338,7 +9847,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="63" spans="2:15" s="18" customFormat="1" ht="54" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="2:15" s="18" customFormat="1" ht="54" customHeight="1" thickBot="1">
       <c r="B63" s="47" t="s">
         <v>256</v>
       </c>
@@ -7348,8 +9857,7 @@
       <c r="D63" s="21" t="s">
         <v>170</v>
       </c>
-      <c r="G63" s="258"/>
-      <c r="H63" s="263" t="s">
+      <c r="H63" s="234" t="s">
         <v>257</v>
       </c>
       <c r="I63" s="92" t="s">
@@ -7368,7 +9876,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="64" spans="2:15" s="18" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:15" s="18" customFormat="1" ht="14.55" customHeight="1">
       <c r="B64" s="75" t="s">
         <v>261</v>
       </c>
@@ -7378,8 +9886,7 @@
       <c r="D64" s="21" t="s">
         <v>170</v>
       </c>
-      <c r="G64" s="258"/>
-      <c r="H64" s="260"/>
+      <c r="H64" s="235"/>
       <c r="I64" s="92" t="s">
         <v>244</v>
       </c>
@@ -7387,7 +9894,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="65" spans="2:14" s="18" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:14" s="18" customFormat="1" ht="14.55" customHeight="1">
       <c r="B65" s="75" t="s">
         <v>262</v>
       </c>
@@ -7397,8 +9904,7 @@
       <c r="D65" s="21" t="s">
         <v>170</v>
       </c>
-      <c r="G65" s="258"/>
-      <c r="H65" s="260"/>
+      <c r="H65" s="235"/>
       <c r="I65" s="92" t="s">
         <v>245</v>
       </c>
@@ -7406,8 +9912,8 @@
         <v>258</v>
       </c>
     </row>
-    <row r="66" spans="2:14" s="18" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B66" s="222" t="s">
+    <row r="66" spans="2:14" s="18" customFormat="1" ht="15" customHeight="1" thickBot="1">
+      <c r="B66" s="237" t="s">
         <v>257</v>
       </c>
       <c r="C66" s="46" t="s">
@@ -7416,8 +9922,7 @@
       <c r="D66" s="21" t="s">
         <v>263</v>
       </c>
-      <c r="G66" s="258"/>
-      <c r="H66" s="245"/>
+      <c r="H66" s="236"/>
       <c r="I66" s="93" t="s">
         <v>246</v>
       </c>
@@ -7425,68 +9930,60 @@
         <v>258</v>
       </c>
     </row>
-    <row r="67" spans="2:14" s="18" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B67" s="220"/>
+    <row r="67" spans="2:14" s="18" customFormat="1" ht="14.55" customHeight="1">
+      <c r="B67" s="238"/>
       <c r="C67" s="46" t="s">
         <v>244</v>
       </c>
       <c r="D67" s="21" t="s">
         <v>263</v>
       </c>
-      <c r="G67" s="258"/>
       <c r="H67" s="66"/>
       <c r="I67" s="66"/>
     </row>
-    <row r="68" spans="2:14" s="18" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B68" s="220"/>
+    <row r="68" spans="2:14" s="18" customFormat="1" ht="14.55" customHeight="1">
+      <c r="B68" s="238"/>
       <c r="C68" s="46" t="s">
         <v>245</v>
       </c>
       <c r="D68" s="21" t="s">
         <v>263</v>
       </c>
-      <c r="G68" s="258"/>
       <c r="H68" s="66"/>
       <c r="I68" s="66"/>
     </row>
-    <row r="69" spans="2:14" s="18" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B69" s="221"/>
+    <row r="69" spans="2:14" s="18" customFormat="1" ht="15" customHeight="1" thickBot="1">
+      <c r="B69" s="239"/>
       <c r="C69" s="73" t="s">
         <v>246</v>
       </c>
       <c r="D69" s="21" t="s">
         <v>263</v>
       </c>
-      <c r="G69" s="258"/>
       <c r="H69" s="66"/>
       <c r="I69" s="66"/>
     </row>
-    <row r="70" spans="2:14" s="18" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="G70" s="258"/>
+    <row r="70" spans="2:14" s="18" customFormat="1" ht="14.55" customHeight="1">
       <c r="H70" s="66"/>
       <c r="I70" s="66"/>
     </row>
-    <row r="71" spans="2:14" s="18" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="G71" s="258"/>
-    </row>
-    <row r="72" spans="2:14" s="25" customFormat="1" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="71" spans="2:14" s="18" customFormat="1" ht="14.55" customHeight="1"/>
+    <row r="72" spans="2:14" s="25" customFormat="1" ht="19.05" customHeight="1" thickBot="1">
       <c r="B72" s="119" t="s">
         <v>8</v>
       </c>
-      <c r="G72" s="266"/>
-    </row>
-    <row r="73" spans="2:14" s="18" customFormat="1" ht="32.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="73" spans="2:14" s="18" customFormat="1" ht="32.1" customHeight="1" thickBot="1">
       <c r="B73" s="116" t="s">
         <v>264</v>
       </c>
       <c r="C73" s="124" t="s">
         <v>119</v>
       </c>
-      <c r="G73" s="258"/>
-      <c r="H73" s="235" t="s">
+      <c r="H73" s="229" t="s">
         <v>265</v>
       </c>
-      <c r="I73" s="212"/>
+      <c r="I73" s="230"/>
       <c r="J73" s="125" t="s">
         <v>119</v>
       </c>
@@ -7500,18 +9997,17 @@
         <v>123</v>
       </c>
     </row>
-    <row r="74" spans="2:14" s="18" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="2:14" s="18" customFormat="1" ht="54" customHeight="1">
       <c r="B74" s="76" t="s">
         <v>198</v>
       </c>
       <c r="C74" s="70" t="s">
         <v>170</v>
       </c>
-      <c r="G74" s="258"/>
-      <c r="H74" s="219" t="s">
+      <c r="H74" s="224" t="s">
         <v>165</v>
       </c>
-      <c r="I74" s="239"/>
+      <c r="I74" s="225"/>
       <c r="J74" s="45" t="s">
         <v>137</v>
       </c>
@@ -7525,18 +10021,17 @@
         <v>267</v>
       </c>
     </row>
-    <row r="75" spans="2:14" s="18" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="2:14" s="18" customFormat="1" ht="54" customHeight="1">
       <c r="B75" s="77" t="s">
         <v>199</v>
       </c>
       <c r="C75" s="68" t="s">
         <v>170</v>
       </c>
-      <c r="G75" s="258"/>
-      <c r="H75" s="215" t="s">
+      <c r="H75" s="220" t="s">
         <v>171</v>
       </c>
-      <c r="I75" s="216"/>
+      <c r="I75" s="221"/>
       <c r="J75" s="21" t="s">
         <v>137</v>
       </c>
@@ -7550,18 +10045,17 @@
         <v>269</v>
       </c>
     </row>
-    <row r="76" spans="2:14" s="18" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="2:14" s="18" customFormat="1" ht="54" customHeight="1">
       <c r="B76" s="77" t="s">
         <v>200</v>
       </c>
       <c r="C76" s="68" t="s">
         <v>170</v>
       </c>
-      <c r="G76" s="258"/>
-      <c r="H76" s="215" t="s">
+      <c r="H76" s="220" t="s">
         <v>270</v>
       </c>
-      <c r="I76" s="216"/>
+      <c r="I76" s="221"/>
       <c r="J76" s="21" t="s">
         <v>137</v>
       </c>
@@ -7575,18 +10069,17 @@
         <v>273</v>
       </c>
     </row>
-    <row r="77" spans="2:14" s="18" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:14" s="18" customFormat="1" ht="54" customHeight="1">
       <c r="B77" s="77" t="s">
         <v>274</v>
       </c>
       <c r="C77" s="68" t="s">
         <v>170</v>
       </c>
-      <c r="G77" s="258"/>
-      <c r="H77" s="215" t="s">
+      <c r="H77" s="220" t="s">
         <v>275</v>
       </c>
-      <c r="I77" s="216"/>
+      <c r="I77" s="221"/>
       <c r="J77" s="21" t="s">
         <v>276</v>
       </c>
@@ -7600,18 +10093,17 @@
         <v>279</v>
       </c>
     </row>
-    <row r="78" spans="2:14" s="18" customFormat="1" ht="54" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="2:14" s="18" customFormat="1" ht="54" customHeight="1" thickBot="1">
       <c r="B78" s="77" t="s">
         <v>280</v>
       </c>
       <c r="C78" s="68" t="s">
         <v>263</v>
       </c>
-      <c r="G78" s="258"/>
-      <c r="H78" s="213" t="s">
+      <c r="H78" s="216" t="s">
         <v>281</v>
       </c>
-      <c r="I78" s="214"/>
+      <c r="I78" s="217"/>
       <c r="J78" s="24" t="s">
         <v>282</v>
       </c>
@@ -7625,43 +10117,37 @@
         <v>285</v>
       </c>
     </row>
-    <row r="79" spans="2:14" s="18" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="2:14" s="18" customFormat="1" ht="15" customHeight="1" thickBot="1">
       <c r="B79" s="78" t="s">
         <v>286</v>
       </c>
       <c r="C79" s="79" t="s">
         <v>263</v>
       </c>
-      <c r="G79" s="258"/>
       <c r="H79" s="66"/>
       <c r="I79" s="66"/>
     </row>
-    <row r="80" spans="2:14" s="18" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="G80" s="258"/>
+    <row r="80" spans="2:14" s="18" customFormat="1" ht="14.55" customHeight="1">
       <c r="H80" s="66"/>
       <c r="I80" s="66"/>
     </row>
-    <row r="81" spans="2:14" s="18" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="G81" s="258"/>
-    </row>
-    <row r="82" spans="2:14" s="25" customFormat="1" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="81" spans="2:14" s="18" customFormat="1" ht="14.55" customHeight="1"/>
+    <row r="82" spans="2:14" s="25" customFormat="1" ht="19.05" customHeight="1" thickBot="1">
       <c r="B82" s="119" t="s">
         <v>287</v>
       </c>
-      <c r="G82" s="266"/>
-    </row>
-    <row r="83" spans="2:14" s="18" customFormat="1" ht="32.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="83" spans="2:14" s="18" customFormat="1" ht="32.1" customHeight="1" thickBot="1">
       <c r="B83" s="116" t="s">
         <v>264</v>
       </c>
       <c r="C83" s="124" t="s">
         <v>119</v>
       </c>
-      <c r="G83" s="258"/>
-      <c r="H83" s="235" t="s">
+      <c r="H83" s="229" t="s">
         <v>118</v>
       </c>
-      <c r="I83" s="212"/>
+      <c r="I83" s="230"/>
       <c r="J83" s="122" t="s">
         <v>119</v>
       </c>
@@ -7675,18 +10161,17 @@
         <v>123</v>
       </c>
     </row>
-    <row r="84" spans="2:14" s="18" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:14" s="18" customFormat="1" ht="54" customHeight="1">
       <c r="B84" s="76" t="s">
         <v>288</v>
       </c>
       <c r="C84" s="70" t="s">
         <v>263</v>
       </c>
-      <c r="G84" s="258"/>
-      <c r="H84" s="219" t="s">
+      <c r="H84" s="224" t="s">
         <v>289</v>
       </c>
-      <c r="I84" s="239"/>
+      <c r="I84" s="225"/>
       <c r="J84" s="74" t="s">
         <v>137</v>
       </c>
@@ -7700,18 +10185,17 @@
         <v>292</v>
       </c>
     </row>
-    <row r="85" spans="2:14" s="18" customFormat="1" ht="54" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="85" spans="2:14" s="18" customFormat="1" ht="54" customHeight="1" thickBot="1">
       <c r="B85" s="77" t="s">
         <v>293</v>
       </c>
       <c r="C85" s="68" t="s">
         <v>263</v>
       </c>
-      <c r="G85" s="258"/>
-      <c r="H85" s="213" t="s">
+      <c r="H85" s="216" t="s">
         <v>294</v>
       </c>
-      <c r="I85" s="214"/>
+      <c r="I85" s="217"/>
       <c r="J85" s="24" t="s">
         <v>137</v>
       </c>
@@ -7725,44 +10209,40 @@
         <v>297</v>
       </c>
     </row>
-    <row r="86" spans="2:14" s="25" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="2:14" s="25" customFormat="1" ht="15" customHeight="1" thickBot="1">
       <c r="B86" s="78" t="s">
         <v>298</v>
       </c>
       <c r="C86" s="79" t="s">
         <v>263</v>
       </c>
-      <c r="G86" s="266"/>
       <c r="H86" s="90"/>
       <c r="I86" s="90"/>
     </row>
-    <row r="87" spans="2:14" s="25" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="2:14" s="25" customFormat="1" ht="14.55" customHeight="1">
       <c r="B87" s="18"/>
       <c r="C87" s="18"/>
-      <c r="G87" s="266"/>
       <c r="H87" s="90"/>
       <c r="I87" s="90"/>
     </row>
-    <row r="88" spans="2:14" s="18" customFormat="1" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="88" spans="2:14" s="18" customFormat="1" ht="19.05" customHeight="1" thickBot="1">
       <c r="B88" s="119" t="s">
         <v>299</v>
       </c>
-      <c r="G88" s="258"/>
       <c r="H88" s="66"/>
       <c r="I88" s="66"/>
     </row>
-    <row r="89" spans="2:14" s="18" customFormat="1" ht="32.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="2:14" s="18" customFormat="1" ht="32.1" customHeight="1" thickBot="1">
       <c r="B89" s="116" t="s">
         <v>264</v>
       </c>
       <c r="C89" s="124" t="s">
         <v>234</v>
       </c>
-      <c r="G89" s="258"/>
-      <c r="H89" s="235" t="s">
+      <c r="H89" s="229" t="s">
         <v>118</v>
       </c>
-      <c r="I89" s="212"/>
+      <c r="I89" s="230"/>
       <c r="J89" s="122" t="s">
         <v>119</v>
       </c>
@@ -7776,18 +10256,17 @@
         <v>123</v>
       </c>
     </row>
-    <row r="90" spans="2:14" s="18" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="2:14" s="18" customFormat="1" ht="54" customHeight="1">
       <c r="B90" s="80" t="s">
         <v>300</v>
       </c>
       <c r="C90" s="81" t="s">
         <v>170</v>
       </c>
-      <c r="G90" s="258"/>
-      <c r="H90" s="237" t="s">
+      <c r="H90" s="222" t="s">
         <v>301</v>
       </c>
-      <c r="I90" s="238"/>
+      <c r="I90" s="223"/>
       <c r="J90" s="83" t="s">
         <v>137</v>
       </c>
@@ -7801,18 +10280,17 @@
         <v>304</v>
       </c>
     </row>
-    <row r="91" spans="2:14" s="18" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="2:14" s="18" customFormat="1" ht="54" customHeight="1">
       <c r="B91" s="77" t="s">
         <v>305</v>
       </c>
       <c r="C91" s="68" t="s">
         <v>170</v>
       </c>
-      <c r="G91" s="258"/>
-      <c r="H91" s="233" t="s">
+      <c r="H91" s="212" t="s">
         <v>306</v>
       </c>
-      <c r="I91" s="234"/>
+      <c r="I91" s="213"/>
       <c r="J91" s="84" t="s">
         <v>137</v>
       </c>
@@ -7826,18 +10304,17 @@
         <v>309</v>
       </c>
     </row>
-    <row r="92" spans="2:14" s="18" customFormat="1" ht="54" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="92" spans="2:14" s="18" customFormat="1" ht="54" customHeight="1" thickBot="1">
       <c r="B92" s="77" t="s">
         <v>310</v>
       </c>
       <c r="C92" s="68" t="s">
         <v>170</v>
       </c>
-      <c r="G92" s="258"/>
-      <c r="H92" s="230" t="s">
+      <c r="H92" s="214" t="s">
         <v>311</v>
       </c>
-      <c r="I92" s="231"/>
+      <c r="I92" s="215"/>
       <c r="J92" s="82" t="s">
         <v>243</v>
       </c>
@@ -7851,98 +10328,89 @@
         <v>314</v>
       </c>
     </row>
-    <row r="93" spans="2:14" s="18" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="2:14" s="18" customFormat="1" ht="14.55" customHeight="1">
       <c r="B93" s="77" t="s">
         <v>315</v>
       </c>
       <c r="C93" s="68" t="s">
         <v>170</v>
       </c>
-      <c r="G93" s="258"/>
       <c r="H93" s="66"/>
       <c r="I93" s="66"/>
     </row>
-    <row r="94" spans="2:14" s="18" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="2:14" s="18" customFormat="1" ht="14.55" customHeight="1">
       <c r="B94" s="77" t="s">
         <v>316</v>
       </c>
       <c r="C94" s="68" t="s">
         <v>317</v>
       </c>
-      <c r="G94" s="258"/>
-    </row>
-    <row r="95" spans="2:14" s="18" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="95" spans="2:14" s="18" customFormat="1" ht="15" customHeight="1" thickBot="1">
       <c r="B95" s="78" t="s">
         <v>318</v>
       </c>
       <c r="C95" s="79" t="s">
         <v>317</v>
       </c>
-      <c r="G95" s="258"/>
-    </row>
-    <row r="96" spans="2:14" s="18" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="G96" s="258"/>
+    </row>
+    <row r="96" spans="2:14" s="18" customFormat="1" ht="45" customHeight="1">
       <c r="L96" s="200" t="s">
         <v>319</v>
       </c>
-      <c r="M96" s="236" t="s">
+      <c r="M96" s="211" t="s">
         <v>320</v>
       </c>
-      <c r="N96" s="236"/>
-    </row>
-    <row r="97" spans="7:7" s="18" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="G97" s="258"/>
-    </row>
-    <row r="98" spans="7:7" s="18" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="G98" s="258"/>
-    </row>
-    <row r="99" spans="7:7" s="18" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="G99" s="258"/>
-    </row>
-    <row r="100" spans="7:7" s="18" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="G100" s="258"/>
-    </row>
-    <row r="101" spans="7:7" s="18" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="G101" s="258"/>
-    </row>
-    <row r="102" spans="7:7" s="18" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="G102" s="258"/>
-    </row>
-    <row r="103" spans="7:7" s="18" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="G103" s="258"/>
-    </row>
-    <row r="104" spans="7:7" s="18" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="G104" s="258"/>
-    </row>
-    <row r="105" spans="7:7" s="18" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="G105" s="258"/>
-    </row>
-    <row r="106" spans="7:7" s="18" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="G106" s="258"/>
-    </row>
-    <row r="107" spans="7:7" s="18" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="G107" s="258"/>
-    </row>
-    <row r="108" spans="7:7" s="18" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="G108" s="258"/>
-    </row>
-    <row r="109" spans="7:7" s="18" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="G109" s="258"/>
-    </row>
-    <row r="110" spans="7:7" s="18" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="G110" s="258"/>
-    </row>
-    <row r="111" spans="7:7" s="18" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="G111" s="258"/>
-    </row>
-    <row r="112" spans="7:7" s="18" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="G112" s="258"/>
-    </row>
-    <row r="113" spans="7:7" s="18" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="G113" s="258"/>
-    </row>
+      <c r="N96" s="211"/>
+    </row>
+    <row r="97" s="18" customFormat="1" ht="14.55" customHeight="1"/>
+    <row r="98" s="18" customFormat="1" ht="14.55" customHeight="1"/>
+    <row r="99" s="18" customFormat="1" ht="14.55" customHeight="1"/>
+    <row r="100" s="18" customFormat="1" ht="14.55" customHeight="1"/>
+    <row r="101" s="18" customFormat="1" ht="14.55" customHeight="1"/>
+    <row r="102" s="18" customFormat="1" ht="14.55" customHeight="1"/>
+    <row r="103" s="18" customFormat="1" ht="14.55" customHeight="1"/>
+    <row r="104" s="18" customFormat="1" ht="14.55" customHeight="1"/>
+    <row r="105" s="18" customFormat="1" ht="14.55" customHeight="1"/>
+    <row r="106" s="18" customFormat="1" ht="14.55" customHeight="1"/>
+    <row r="107" s="18" customFormat="1" ht="14.55" customHeight="1"/>
+    <row r="108" s="18" customFormat="1" ht="14.55" customHeight="1"/>
+    <row r="109" s="18" customFormat="1" ht="14.55" customHeight="1"/>
+    <row r="110" s="18" customFormat="1" ht="14.55" customHeight="1"/>
+    <row r="111" s="18" customFormat="1" ht="14.55" customHeight="1"/>
+    <row r="112" s="18" customFormat="1" ht="14.55" customHeight="1"/>
+    <row r="113" s="18" customFormat="1" ht="14.55" customHeight="1"/>
   </sheetData>
   <mergeCells count="45">
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="H77:I77"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="H57:H60"/>
+    <mergeCell ref="B45:B47"/>
+    <mergeCell ref="B58:B61"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="N3:N4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="H92:I92"/>
+    <mergeCell ref="B43:E43"/>
+    <mergeCell ref="H45:I45"/>
+    <mergeCell ref="H89:I89"/>
+    <mergeCell ref="H63:H66"/>
+    <mergeCell ref="H73:I73"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="B66:B69"/>
+    <mergeCell ref="H43:I43"/>
     <mergeCell ref="M96:N96"/>
     <mergeCell ref="H91:I91"/>
     <mergeCell ref="H47:I47"/>
@@ -7959,66 +10427,37 @@
     <mergeCell ref="H78:I78"/>
     <mergeCell ref="H74:I74"/>
     <mergeCell ref="H83:I83"/>
-    <mergeCell ref="H92:I92"/>
-    <mergeCell ref="B43:E43"/>
-    <mergeCell ref="H45:I45"/>
-    <mergeCell ref="H89:I89"/>
-    <mergeCell ref="H63:H66"/>
-    <mergeCell ref="H73:I73"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="B66:B69"/>
-    <mergeCell ref="H43:I43"/>
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="N3:N4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="K3:K4"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="H77:I77"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="H57:H60"/>
-    <mergeCell ref="B45:B47"/>
-    <mergeCell ref="B58:B61"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="H14:I14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A5:H25"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="63.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.453125" customWidth="1"/>
-    <col min="3" max="3" width="22.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26.1796875" customWidth="1"/>
-    <col min="5" max="5" width="41.1796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="63.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.44140625" customWidth="1"/>
+    <col min="3" max="3" width="22.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.21875" customWidth="1"/>
+    <col min="5" max="5" width="41.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="6" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:8" ht="15" customHeight="1" thickBot="1"/>
+    <row r="6" spans="1:8" ht="15" customHeight="1" thickBot="1">
       <c r="A6" s="143" t="s">
         <v>321</v>
       </c>
       <c r="B6" s="144"/>
-      <c r="C6" s="243"/>
-      <c r="D6" s="210"/>
-      <c r="E6" s="210"/>
-      <c r="F6" s="208"/>
-    </row>
-    <row r="7" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C6" s="254"/>
+      <c r="D6" s="232"/>
+      <c r="E6" s="232"/>
+      <c r="F6" s="233"/>
+    </row>
+    <row r="7" spans="1:8" ht="15" customHeight="1" thickBot="1">
       <c r="A7" s="126" t="s">
         <v>322</v>
       </c>
@@ -8038,7 +10477,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8">
       <c r="A8" s="55" t="s">
         <v>327</v>
       </c>
@@ -8050,7 +10489,7 @@
       </c>
       <c r="F8" s="57"/>
     </row>
-    <row r="9" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:8" ht="15" customHeight="1" thickBot="1">
       <c r="A9" s="52"/>
       <c r="B9" s="53"/>
       <c r="C9" s="53"/>
@@ -8058,19 +10497,19 @@
       <c r="E9" s="54"/>
       <c r="F9" s="54"/>
     </row>
-    <row r="11" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="244" t="s">
+    <row r="11" spans="1:8" ht="15" customHeight="1" thickBot="1">
+      <c r="A11" s="255" t="s">
         <v>329</v>
       </c>
-      <c r="B11" s="245"/>
-      <c r="C11" s="245"/>
-      <c r="D11" s="245"/>
-      <c r="E11" s="245"/>
-      <c r="F11" s="245"/>
-      <c r="G11" s="245"/>
-      <c r="H11" s="246"/>
-    </row>
-    <row r="12" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B11" s="236"/>
+      <c r="C11" s="236"/>
+      <c r="D11" s="236"/>
+      <c r="E11" s="236"/>
+      <c r="F11" s="236"/>
+      <c r="G11" s="236"/>
+      <c r="H11" s="256"/>
+    </row>
+    <row r="12" spans="1:8" ht="15" customHeight="1" thickBot="1">
       <c r="A12" s="126" t="s">
         <v>322</v>
       </c>
@@ -8096,7 +10535,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8">
       <c r="A13" s="55" t="s">
         <v>332</v>
       </c>
@@ -8118,7 +10557,7 @@
       <c r="G13" s="96"/>
       <c r="H13" s="146"/>
     </row>
-    <row r="14" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:8" ht="15" customHeight="1" thickBot="1">
       <c r="A14" s="52"/>
       <c r="B14" s="53"/>
       <c r="C14" s="53"/>
@@ -8128,8 +10567,8 @@
       <c r="G14" s="6"/>
       <c r="H14" s="147"/>
     </row>
-    <row r="16" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="17" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:8" ht="15" customHeight="1" thickBot="1"/>
+    <row r="17" spans="1:8" ht="15" customHeight="1" thickBot="1">
       <c r="A17" s="149" t="s">
         <v>333</v>
       </c>
@@ -8137,7 +10576,7 @@
       <c r="C17" s="151"/>
       <c r="D17" s="151"/>
     </row>
-    <row r="18" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:8" ht="15" customHeight="1" thickBot="1">
       <c r="A18" s="126" t="s">
         <v>334</v>
       </c>
@@ -8151,20 +10590,20 @@
         <v>337</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8">
       <c r="A19" s="55"/>
       <c r="B19" s="56"/>
       <c r="C19" s="57"/>
       <c r="D19" s="57"/>
     </row>
-    <row r="20" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:8" ht="15" customHeight="1" thickBot="1">
       <c r="A20" s="52"/>
       <c r="B20" s="53"/>
       <c r="C20" s="54"/>
       <c r="D20" s="54"/>
     </row>
-    <row r="21" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="22" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:8" ht="15" customHeight="1" thickBot="1"/>
+    <row r="22" spans="1:8" ht="15" customHeight="1" thickBot="1">
       <c r="A22" s="149" t="s">
         <v>338</v>
       </c>
@@ -8176,7 +10615,7 @@
       <c r="G22" s="150"/>
       <c r="H22" s="151"/>
     </row>
-    <row r="23" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:8" ht="15" customHeight="1" thickBot="1">
       <c r="A23" s="126" t="s">
         <v>334</v>
       </c>
@@ -8202,7 +10641,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8">
       <c r="A24" s="55" t="s">
         <v>332</v>
       </c>
@@ -8222,7 +10661,7 @@
       </c>
       <c r="H24" s="57"/>
     </row>
-    <row r="25" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:8" ht="15" customHeight="1" thickBot="1">
       <c r="A25" s="52"/>
       <c r="B25" s="53"/>
       <c r="C25" s="54"/>
@@ -8239,466 +10678,4 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="C4:G33"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="3" max="3" width="24.1796875" customWidth="1"/>
-    <col min="4" max="4" width="23.81640625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="4" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C4" s="129" t="s">
-        <v>344</v>
-      </c>
-      <c r="D4" s="129" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C5" s="31" t="s">
-        <v>345</v>
-      </c>
-      <c r="D5" s="31" t="s">
-        <v>346</v>
-      </c>
-      <c r="E5" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="6" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C6" s="31" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" s="31" t="s">
-        <v>348</v>
-      </c>
-      <c r="E6" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="7" spans="3:5" ht="101.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C7" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="D7" s="31" t="s">
-        <v>55</v>
-      </c>
-      <c r="E7" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="8" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C8" s="31" t="s">
-        <v>350</v>
-      </c>
-      <c r="D8" s="31" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="9" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C9" s="31" t="s">
-        <v>352</v>
-      </c>
-      <c r="D9" s="31" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="10" spans="3:5" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C10" s="31" t="s">
-        <v>354</v>
-      </c>
-      <c r="D10" s="31" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="11" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C11" s="31" t="s">
-        <v>356</v>
-      </c>
-      <c r="D11" s="31" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="12" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C12" s="31" t="s">
-        <v>358</v>
-      </c>
-      <c r="D12" s="31" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="13" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C13" s="31" t="s">
-        <v>360</v>
-      </c>
-      <c r="D13" s="31" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="14" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C14" s="31" t="s">
-        <v>362</v>
-      </c>
-      <c r="D14" s="31" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="15" spans="3:5" ht="29.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C15" s="31" t="s">
-        <v>364</v>
-      </c>
-      <c r="D15" s="31" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="16" spans="3:5" ht="29.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C16" s="31" t="s">
-        <v>366</v>
-      </c>
-      <c r="D16" s="31" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="17" spans="3:7" ht="29.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C17" s="31" t="s">
-        <v>368</v>
-      </c>
-      <c r="D17" s="31" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="18" spans="3:7" x14ac:dyDescent="0.35">
-      <c r="C18" s="31" t="s">
-        <v>370</v>
-      </c>
-      <c r="D18" s="31" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="19" spans="3:7" x14ac:dyDescent="0.35">
-      <c r="C19" s="31" t="s">
-        <v>372</v>
-      </c>
-      <c r="D19" s="31" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="20" spans="3:7" x14ac:dyDescent="0.35">
-      <c r="C20" s="31" t="s">
-        <v>374</v>
-      </c>
-      <c r="D20" s="31" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="21" spans="3:7" x14ac:dyDescent="0.35">
-      <c r="C21" s="31" t="s">
-        <v>376</v>
-      </c>
-      <c r="D21" s="31" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="22" spans="3:7" ht="29.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C22" s="31" t="s">
-        <v>378</v>
-      </c>
-      <c r="D22" s="31" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="23" spans="3:7" x14ac:dyDescent="0.35">
-      <c r="C23" s="31" t="s">
-        <v>380</v>
-      </c>
-      <c r="D23" s="31" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="24" spans="3:7" x14ac:dyDescent="0.35">
-      <c r="C24" s="31" t="s">
-        <v>382</v>
-      </c>
-      <c r="D24" s="31" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="25" spans="3:7" ht="29.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C25" s="31" t="s">
-        <v>384</v>
-      </c>
-      <c r="D25" s="31" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="26" spans="3:7" x14ac:dyDescent="0.35">
-      <c r="C26" s="31" t="s">
-        <v>386</v>
-      </c>
-      <c r="D26" s="31" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="27" spans="3:7" x14ac:dyDescent="0.35">
-      <c r="C27" s="31" t="s">
-        <v>388</v>
-      </c>
-      <c r="D27" s="31" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="28" spans="3:7" x14ac:dyDescent="0.35">
-      <c r="C28" s="31" t="s">
-        <v>390</v>
-      </c>
-      <c r="D28" s="31" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="29" spans="3:7" x14ac:dyDescent="0.35">
-      <c r="C29" s="31" t="s">
-        <v>392</v>
-      </c>
-      <c r="D29" s="31" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="30" spans="3:7" x14ac:dyDescent="0.35">
-      <c r="C30" s="31" t="s">
-        <v>394</v>
-      </c>
-      <c r="D30" s="31" t="s">
-        <v>395</v>
-      </c>
-      <c r="G30" s="33"/>
-    </row>
-    <row r="31" spans="3:7" x14ac:dyDescent="0.35">
-      <c r="C31" s="31" t="s">
-        <v>396</v>
-      </c>
-      <c r="D31" s="31" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="32" spans="3:7" x14ac:dyDescent="0.35">
-      <c r="C32" s="31" t="s">
-        <v>398</v>
-      </c>
-      <c r="D32" s="31" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="33" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C33" s="31" t="s">
-        <v>342</v>
-      </c>
-      <c r="D33" s="31" t="s">
-        <v>400</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="B3:C25"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="2" max="2" width="15.7265625" customWidth="1"/>
-    <col min="3" max="3" width="24.1796875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B3" s="129" t="s">
-        <v>344</v>
-      </c>
-      <c r="C3" s="129" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B4" s="31" t="s">
-        <v>401</v>
-      </c>
-      <c r="C4" s="31" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B5" s="31" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" s="31" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="6" spans="2:3" ht="101.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="C6" s="31" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B7" s="31" t="s">
-        <v>402</v>
-      </c>
-      <c r="C7" s="31" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="8" spans="2:3" ht="29.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="31" t="s">
-        <v>403</v>
-      </c>
-      <c r="C8" s="31" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="9" spans="2:3" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="31" t="s">
-        <v>404</v>
-      </c>
-      <c r="C9" s="31" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="10" spans="2:3" ht="29.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="31" t="s">
-        <v>358</v>
-      </c>
-      <c r="C10" s="31" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B11" s="31" t="s">
-        <v>360</v>
-      </c>
-      <c r="C11" s="31" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="12" spans="2:3" ht="29.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="31" t="s">
-        <v>406</v>
-      </c>
-      <c r="C12" s="31" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="13" spans="2:3" ht="29.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="31" t="s">
-        <v>368</v>
-      </c>
-      <c r="C13" s="31" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="14" spans="2:3" ht="29.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="31" t="s">
-        <v>408</v>
-      </c>
-      <c r="C14" s="31" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="15" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B15" s="31" t="s">
-        <v>410</v>
-      </c>
-      <c r="C15" s="31" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="16" spans="2:3" ht="58" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="31" t="s">
-        <v>412</v>
-      </c>
-      <c r="C16" s="31" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3" ht="29.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="31" t="s">
-        <v>414</v>
-      </c>
-      <c r="C17" s="31" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B18" s="31" t="s">
-        <v>416</v>
-      </c>
-      <c r="C18" s="31" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="19" spans="2:3" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="31" t="s">
-        <v>418</v>
-      </c>
-      <c r="C19" s="31" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="20" spans="2:3" ht="29.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="31" t="s">
-        <v>341</v>
-      </c>
-      <c r="C20" s="31" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="21" spans="2:3" ht="29.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="31" t="s">
-        <v>420</v>
-      </c>
-      <c r="C21" s="31" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B22" s="31" t="s">
-        <v>421</v>
-      </c>
-      <c r="C22" s="31" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B23" s="31" t="s">
-        <v>423</v>
-      </c>
-      <c r="C23" s="31" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B24" s="31" t="s">
-        <v>398</v>
-      </c>
-      <c r="C24" s="31" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B25" s="31" t="s">
-        <v>342</v>
-      </c>
-      <c r="C25" s="31" t="s">
-        <v>400</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>